--- a/07_Model/SpaceX Valuation Model v26.06.11 (Pre-IPO).xlsx
+++ b/07_Model/SpaceX Valuation Model v26.06.11 (Pre-IPO).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Personal Finances\4-Trades &amp; Investments\Valuation Models\$SPCX - Space Exploration Technologies Corp\07_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9443D32-AFD5-471E-863C-0D8F8F8A4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B520D8-C626-436F-A73D-F3577D97866F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="877" xr2:uid="{80111FE1-D860-9C46-9D05-D269D00C2A2F}"/>
   </bookViews>
@@ -17232,7 +17232,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="792">
   <si>
     <t>Revenue ($M)</t>
   </si>
@@ -19605,6 +19605,9 @@
   </si>
   <si>
     <t>Comp Data Status</t>
+  </si>
+  <si>
+    <t>Rifat Tahmid</t>
   </si>
 </sst>
 </file>
@@ -19630,7 +19633,7 @@
     <numFmt numFmtId="179" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="180" formatCode="0.0%;\(0.0%\)"/>
   </numFmts>
-  <fonts count="78" x14ac:knownFonts="1">
+  <fonts count="79">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -20154,6 +20157,13 @@
       <color rgb="FF008000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -20474,7 +20484,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="356">
+  <cellXfs count="357">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -21227,34 +21237,35 @@
     <xf numFmtId="0" fontId="76" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="68" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -23489,8 +23500,8 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J100"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="48.109375" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
@@ -23500,36 +23511,36 @@
     <col min="7" max="7" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="342" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="345" t="s">
         <v>763</v>
       </c>
-      <c r="B1" s="343"/>
-      <c r="C1" s="343"/>
-      <c r="D1" s="343"/>
-      <c r="E1" s="343"/>
-      <c r="F1" s="343"/>
-      <c r="G1" s="343"/>
-      <c r="H1" s="343"/>
-      <c r="I1" s="343"/>
-      <c r="J1" s="343"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="344" t="str">
+      <c r="B1" s="346"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="347" t="str">
         <f ca="1">"Prepared: "&amp;TEXT(TODAY(),"d-mmm-yyyy")&amp;"  |  Source: SpaceX S-1 (Filed 20-May-2026) "</f>
         <v xml:space="preserve">Prepared: 11-Jun-2026  |  Source: SpaceX S-1 (Filed 20-May-2026) </v>
       </c>
-      <c r="B2" s="345"/>
-      <c r="C2" s="345"/>
-      <c r="D2" s="345"/>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
-      <c r="G2" s="345"/>
-      <c r="H2" s="345"/>
-      <c r="I2" s="345"/>
-      <c r="J2" s="345"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="348"/>
+      <c r="C2" s="348"/>
+      <c r="D2" s="348"/>
+      <c r="E2" s="348"/>
+      <c r="F2" s="348"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="348"/>
+      <c r="I2" s="348"/>
+      <c r="J2" s="348"/>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="252"/>
       <c r="B3" s="252"/>
       <c r="C3" s="252"/>
@@ -23537,7 +23548,7 @@
       <c r="E3" s="252"/>
       <c r="F3" s="252"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="A4" s="253" t="s">
         <v>668</v>
       </c>
@@ -23551,7 +23562,7 @@
       <c r="I4" s="254"/>
       <c r="J4" s="254"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10">
       <c r="A5" s="252"/>
       <c r="B5" s="252"/>
       <c r="C5" s="252"/>
@@ -23559,7 +23570,7 @@
       <c r="E5" s="252"/>
       <c r="F5" s="252"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10">
       <c r="A6" s="252" t="s">
         <v>669</v>
       </c>
@@ -23569,7 +23580,7 @@
       <c r="E6" s="252"/>
       <c r="F6" s="252"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7" s="255" t="s">
         <v>670</v>
       </c>
@@ -23579,7 +23590,7 @@
       <c r="E7" s="252"/>
       <c r="F7" s="252"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10">
       <c r="A8" s="255" t="s">
         <v>671</v>
       </c>
@@ -23589,7 +23600,7 @@
       <c r="E8" s="252"/>
       <c r="F8" s="252"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="255" t="s">
         <v>672</v>
       </c>
@@ -23599,7 +23610,7 @@
       <c r="E9" s="252"/>
       <c r="F9" s="252"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" s="252"/>
       <c r="B10" s="252"/>
       <c r="C10" s="252"/>
@@ -23607,7 +23618,7 @@
       <c r="E10" s="252"/>
       <c r="F10" s="252"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" s="252" t="s">
         <v>673</v>
       </c>
@@ -23617,7 +23628,7 @@
       <c r="E11" s="252"/>
       <c r="F11" s="252"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" s="252" t="s">
         <v>674</v>
       </c>
@@ -23627,7 +23638,7 @@
       <c r="E12" s="252"/>
       <c r="F12" s="252"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" s="252"/>
       <c r="B13" s="252"/>
       <c r="C13" s="252"/>
@@ -23635,7 +23646,7 @@
       <c r="E13" s="252"/>
       <c r="F13" s="252"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="253" t="s">
         <v>675</v>
       </c>
@@ -23649,7 +23660,7 @@
       <c r="I14" s="254"/>
       <c r="J14" s="254"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="A15" s="256"/>
       <c r="B15" s="257" t="s">
         <v>676</v>
@@ -23669,7 +23680,7 @@
       <c r="I15" s="258"/>
       <c r="J15" s="258"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="300" t="s">
         <v>679</v>
       </c>
@@ -23694,7 +23705,7 @@
       <c r="I16" s="303"/>
       <c r="J16" s="303"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="271" t="s">
         <v>205</v>
       </c>
@@ -23719,7 +23730,7 @@
       <c r="I17" s="304"/>
       <c r="J17" s="304"/>
     </row>
-    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15.6">
       <c r="A18" s="305" t="s">
         <v>680</v>
       </c>
@@ -23744,7 +23755,7 @@
       <c r="I18" s="304"/>
       <c r="J18" s="304"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10">
       <c r="A19" s="307" t="s">
         <v>681</v>
       </c>
@@ -23767,7 +23778,7 @@
       <c r="I19" s="286"/>
       <c r="J19" s="286"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="271" t="s">
         <v>682</v>
       </c>
@@ -23790,7 +23801,7 @@
       <c r="I20" s="286"/>
       <c r="J20" s="286"/>
     </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="15" thickBot="1">
       <c r="A21" s="310" t="s">
         <v>683</v>
       </c>
@@ -23807,7 +23818,7 @@
       <c r="I21" s="312"/>
       <c r="J21" s="312"/>
     </row>
-    <row r="22" spans="1:10" ht="6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="6" customHeight="1" thickTop="1" thickBot="1">
       <c r="A22" s="252"/>
       <c r="B22" s="252"/>
       <c r="C22" s="252"/>
@@ -23819,7 +23830,7 @@
       <c r="I22" s="252"/>
       <c r="J22" s="252"/>
     </row>
-    <row r="23" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="15" thickTop="1">
       <c r="A23" s="293" t="s">
         <v>688</v>
       </c>
@@ -23833,7 +23844,7 @@
       <c r="I23" s="242"/>
       <c r="J23" s="242"/>
     </row>
-    <row r="24" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="6" customHeight="1">
       <c r="A24" s="252"/>
       <c r="B24" s="252"/>
       <c r="C24" s="252"/>
@@ -23841,7 +23852,7 @@
       <c r="E24" s="252"/>
       <c r="F24" s="252"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10">
       <c r="A25" s="269" t="s">
         <v>19</v>
       </c>
@@ -23865,7 +23876,7 @@
       <c r="I25" s="269"/>
       <c r="J25" s="269"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="271" t="s">
         <v>35</v>
       </c>
@@ -23893,7 +23904,7 @@
       <c r="I26" s="275"/>
       <c r="J26" s="275"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10">
       <c r="A27" s="271" t="s">
         <v>152</v>
       </c>
@@ -23921,7 +23932,7 @@
       <c r="I27" s="275"/>
       <c r="J27" s="275"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" s="276" t="s">
         <v>153</v>
       </c>
@@ -23949,7 +23960,7 @@
       <c r="I28" s="280"/>
       <c r="J28" s="280"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" s="281" t="s">
         <v>695</v>
       </c>
@@ -23969,7 +23980,7 @@
       <c r="I29" s="284"/>
       <c r="J29" s="284"/>
     </row>
-    <row r="30" spans="1:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="6" customHeight="1" thickBot="1">
       <c r="A30" s="252"/>
       <c r="B30" s="252"/>
       <c r="C30" s="252"/>
@@ -23977,7 +23988,7 @@
       <c r="E30" s="252"/>
       <c r="F30" s="252"/>
     </row>
-    <row r="31" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="15" thickTop="1">
       <c r="A31" s="293" t="s">
         <v>696</v>
       </c>
@@ -23991,7 +24002,7 @@
       <c r="I31" s="242"/>
       <c r="J31" s="242"/>
     </row>
-    <row r="32" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="6" customHeight="1">
       <c r="A32" s="252"/>
       <c r="B32" s="252"/>
       <c r="C32" s="252"/>
@@ -23999,7 +24010,7 @@
       <c r="E32" s="252"/>
       <c r="F32" s="252"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10">
       <c r="A33" s="269" t="s">
         <v>6</v>
       </c>
@@ -24021,7 +24032,7 @@
       <c r="I33" s="269"/>
       <c r="J33" s="269"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10">
       <c r="A34" s="286" t="s">
         <v>697</v>
       </c>
@@ -24043,7 +24054,7 @@
       <c r="I34" s="275"/>
       <c r="J34" s="275"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" s="286" t="s">
         <v>57</v>
       </c>
@@ -24068,7 +24079,7 @@
       <c r="I35" s="275"/>
       <c r="J35" s="275"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" s="286" t="s">
         <v>82</v>
       </c>
@@ -24093,7 +24104,7 @@
       <c r="I36" s="275"/>
       <c r="J36" s="275"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="286" t="s">
         <v>702</v>
       </c>
@@ -24112,7 +24123,7 @@
       <c r="I37" s="275"/>
       <c r="J37" s="275"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10">
       <c r="A38" s="286" t="s">
         <v>11</v>
       </c>
@@ -24131,7 +24142,7 @@
       <c r="I38" s="275"/>
       <c r="J38" s="275"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="288" t="s">
         <v>13</v>
       </c>
@@ -24150,7 +24161,7 @@
       <c r="I39" s="280"/>
       <c r="J39" s="280"/>
     </row>
-    <row r="40" spans="1:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="6" customHeight="1" thickBot="1">
       <c r="A40" s="252"/>
       <c r="B40" s="252"/>
       <c r="C40" s="252"/>
@@ -24158,7 +24169,7 @@
       <c r="E40" s="252"/>
       <c r="F40" s="252"/>
     </row>
-    <row r="41" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="15" thickTop="1">
       <c r="A41" s="293" t="s">
         <v>706</v>
       </c>
@@ -24172,7 +24183,7 @@
       <c r="I41" s="242"/>
       <c r="J41" s="242"/>
     </row>
-    <row r="42" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="6" customHeight="1">
       <c r="A42" s="252"/>
       <c r="B42" s="252"/>
       <c r="C42" s="252"/>
@@ -24180,7 +24191,7 @@
       <c r="E42" s="252"/>
       <c r="F42" s="252"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="269" t="s">
         <v>174</v>
       </c>
@@ -24200,7 +24211,7 @@
       <c r="I43" s="269"/>
       <c r="J43" s="269"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="271" t="s">
         <v>1</v>
       </c>
@@ -24222,7 +24233,7 @@
       <c r="I44" s="275"/>
       <c r="J44" s="275"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="290" t="s">
         <v>620</v>
       </c>
@@ -24244,7 +24255,7 @@
       <c r="I45" s="275"/>
       <c r="J45" s="275"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46" s="290" t="s">
         <v>619</v>
       </c>
@@ -24266,7 +24277,7 @@
       <c r="I46" s="275"/>
       <c r="J46" s="275"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10">
       <c r="A47" s="290" t="s">
         <v>621</v>
       </c>
@@ -24288,7 +24299,7 @@
       <c r="I47" s="275"/>
       <c r="J47" s="275"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="286" t="s">
         <v>712</v>
       </c>
@@ -24307,7 +24318,7 @@
       <c r="I48" s="275"/>
       <c r="J48" s="275"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10">
       <c r="A49" s="286" t="s">
         <v>185</v>
       </c>
@@ -24326,7 +24337,7 @@
       <c r="I49" s="275"/>
       <c r="J49" s="275"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="286" t="s">
         <v>183</v>
       </c>
@@ -24345,7 +24356,7 @@
       <c r="I50" s="275"/>
       <c r="J50" s="275"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" s="288" t="s">
         <v>188</v>
       </c>
@@ -24364,7 +24375,7 @@
       <c r="I51" s="280"/>
       <c r="J51" s="280"/>
     </row>
-    <row r="52" spans="1:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="6" customHeight="1" thickBot="1">
       <c r="A52" s="252"/>
       <c r="B52" s="252"/>
       <c r="C52" s="252"/>
@@ -24372,7 +24383,7 @@
       <c r="E52" s="252"/>
       <c r="F52" s="252"/>
     </row>
-    <row r="53" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15" thickTop="1">
       <c r="A53" s="293" t="s">
         <v>717</v>
       </c>
@@ -24386,7 +24397,7 @@
       <c r="I53" s="242"/>
       <c r="J53" s="242"/>
     </row>
-    <row r="54" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" ht="6" customHeight="1">
       <c r="A54" s="252"/>
       <c r="B54" s="252"/>
       <c r="C54" s="252"/>
@@ -24394,7 +24405,7 @@
       <c r="E54" s="252"/>
       <c r="F54" s="252"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" s="269" t="s">
         <v>718</v>
       </c>
@@ -24408,7 +24419,7 @@
       <c r="I55" s="269"/>
       <c r="J55" s="269"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" s="290" t="s">
         <v>719</v>
       </c>
@@ -24427,7 +24438,7 @@
       <c r="I56" s="286"/>
       <c r="J56" s="286"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" s="290" t="s">
         <v>721</v>
       </c>
@@ -24446,7 +24457,7 @@
       <c r="I57" s="286"/>
       <c r="J57" s="286"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="322" t="s">
         <v>722</v>
       </c>
@@ -24465,7 +24476,7 @@
       <c r="I58" s="288"/>
       <c r="J58" s="288"/>
     </row>
-    <row r="59" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" ht="6" customHeight="1">
       <c r="A59" s="252"/>
       <c r="B59" s="252"/>
       <c r="C59" s="252"/>
@@ -24473,7 +24484,7 @@
       <c r="E59" s="252"/>
       <c r="F59" s="252"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10">
       <c r="A60" s="269" t="s">
         <v>724</v>
       </c>
@@ -24491,7 +24502,7 @@
       <c r="I60" s="269"/>
       <c r="J60" s="269"/>
     </row>
-    <row r="61" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="14.4" customHeight="1">
       <c r="A61" s="313" t="s">
         <v>726</v>
       </c>
@@ -24509,7 +24520,7 @@
       <c r="I61" s="295"/>
       <c r="J61" s="295"/>
     </row>
-    <row r="62" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="14.4" customHeight="1">
       <c r="A62" s="313" t="s">
         <v>728</v>
       </c>
@@ -24527,7 +24538,7 @@
       <c r="I62" s="295"/>
       <c r="J62" s="295"/>
     </row>
-    <row r="63" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="14.4" customHeight="1">
       <c r="A63" s="313" t="s">
         <v>730</v>
       </c>
@@ -24545,7 +24556,7 @@
       <c r="I63" s="295"/>
       <c r="J63" s="295"/>
     </row>
-    <row r="64" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="14.4" customHeight="1">
       <c r="A64" s="313" t="s">
         <v>733</v>
       </c>
@@ -24563,7 +24574,7 @@
       <c r="I64" s="295"/>
       <c r="J64" s="295"/>
     </row>
-    <row r="65" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="14.4" customHeight="1">
       <c r="A65" s="313" t="s">
         <v>736</v>
       </c>
@@ -24581,7 +24592,7 @@
       <c r="I65" s="295"/>
       <c r="J65" s="295"/>
     </row>
-    <row r="66" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" ht="14.4" customHeight="1">
       <c r="A66" s="314" t="s">
         <v>738</v>
       </c>
@@ -24599,7 +24610,7 @@
       <c r="I66" s="296"/>
       <c r="J66" s="296"/>
     </row>
-    <row r="67" spans="1:10" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" ht="6" customHeight="1" thickBot="1">
       <c r="A67" s="252"/>
       <c r="B67" s="252"/>
       <c r="C67" s="252"/>
@@ -24607,7 +24618,7 @@
       <c r="E67" s="252"/>
       <c r="F67" s="252"/>
     </row>
-    <row r="68" spans="1:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="15" thickTop="1">
       <c r="A68" s="293" t="s">
         <v>740</v>
       </c>
@@ -24621,7 +24632,7 @@
       <c r="I68" s="242"/>
       <c r="J68" s="242"/>
     </row>
-    <row r="69" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="6" customHeight="1">
       <c r="A69" s="252"/>
       <c r="B69" s="252"/>
       <c r="C69" s="252"/>
@@ -24629,199 +24640,224 @@
       <c r="E69" s="252"/>
       <c r="F69" s="252"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A70" s="349" t="s">
+    <row r="70" spans="1:10">
+      <c r="A70" s="340" t="s">
         <v>741</v>
       </c>
-      <c r="B70" s="349"/>
-      <c r="C70" s="349" t="s">
+      <c r="B70" s="340"/>
+      <c r="C70" s="340" t="s">
         <v>742</v>
       </c>
-      <c r="D70" s="349"/>
-      <c r="E70" s="349"/>
-      <c r="F70" s="349"/>
-      <c r="G70" s="349"/>
-      <c r="H70" s="349"/>
-      <c r="I70" s="349"/>
-      <c r="J70" s="349"/>
-    </row>
-    <row r="71" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="346" t="s">
+      <c r="D70" s="340"/>
+      <c r="E70" s="340"/>
+      <c r="F70" s="340"/>
+      <c r="G70" s="340"/>
+      <c r="H70" s="340"/>
+      <c r="I70" s="340"/>
+      <c r="J70" s="340"/>
+    </row>
+    <row r="71" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A71" s="344" t="s">
         <v>743</v>
       </c>
-      <c r="B71" s="346"/>
-      <c r="C71" s="340" t="s">
+      <c r="B71" s="344"/>
+      <c r="C71" s="341" t="s">
         <v>744</v>
       </c>
-      <c r="D71" s="340"/>
-      <c r="E71" s="340"/>
-      <c r="F71" s="340"/>
-      <c r="G71" s="340"/>
-      <c r="H71" s="340"/>
-      <c r="I71" s="340"/>
-      <c r="J71" s="340"/>
-    </row>
-    <row r="72" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="346" t="s">
+      <c r="D71" s="341"/>
+      <c r="E71" s="341"/>
+      <c r="F71" s="341"/>
+      <c r="G71" s="341"/>
+      <c r="H71" s="341"/>
+      <c r="I71" s="341"/>
+      <c r="J71" s="341"/>
+    </row>
+    <row r="72" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A72" s="344" t="s">
         <v>745</v>
       </c>
-      <c r="B72" s="346"/>
-      <c r="C72" s="340" t="s">
+      <c r="B72" s="344"/>
+      <c r="C72" s="341" t="s">
         <v>746</v>
       </c>
-      <c r="D72" s="340"/>
-      <c r="E72" s="340"/>
-      <c r="F72" s="340"/>
-      <c r="G72" s="340"/>
-      <c r="H72" s="340"/>
-      <c r="I72" s="340"/>
-      <c r="J72" s="340"/>
-    </row>
-    <row r="73" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="346" t="s">
+      <c r="D72" s="341"/>
+      <c r="E72" s="341"/>
+      <c r="F72" s="341"/>
+      <c r="G72" s="341"/>
+      <c r="H72" s="341"/>
+      <c r="I72" s="341"/>
+      <c r="J72" s="341"/>
+    </row>
+    <row r="73" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A73" s="344" t="s">
         <v>747</v>
       </c>
-      <c r="B73" s="346"/>
-      <c r="C73" s="340" t="s">
+      <c r="B73" s="344"/>
+      <c r="C73" s="341" t="s">
         <v>748</v>
       </c>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-      <c r="G73" s="340"/>
-      <c r="H73" s="340"/>
-      <c r="I73" s="340"/>
-      <c r="J73" s="340"/>
-    </row>
-    <row r="74" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="346" t="s">
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
+      <c r="G73" s="341"/>
+      <c r="H73" s="341"/>
+      <c r="I73" s="341"/>
+      <c r="J73" s="341"/>
+    </row>
+    <row r="74" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A74" s="344" t="s">
         <v>749</v>
       </c>
-      <c r="B74" s="346"/>
-      <c r="C74" s="340" t="s">
+      <c r="B74" s="344"/>
+      <c r="C74" s="341" t="s">
         <v>750</v>
       </c>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
-      <c r="G74" s="340"/>
-      <c r="H74" s="340"/>
-      <c r="I74" s="340"/>
-      <c r="J74" s="340"/>
-    </row>
-    <row r="75" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="346" t="s">
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
+      <c r="G74" s="341"/>
+      <c r="H74" s="341"/>
+      <c r="I74" s="341"/>
+      <c r="J74" s="341"/>
+    </row>
+    <row r="75" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A75" s="344" t="s">
         <v>751</v>
       </c>
-      <c r="B75" s="346"/>
-      <c r="C75" s="340" t="s">
+      <c r="B75" s="344"/>
+      <c r="C75" s="341" t="s">
         <v>752</v>
       </c>
-      <c r="D75" s="340"/>
-      <c r="E75" s="340"/>
-      <c r="F75" s="340"/>
-      <c r="G75" s="340"/>
-      <c r="H75" s="340"/>
-      <c r="I75" s="340"/>
-      <c r="J75" s="340"/>
-    </row>
-    <row r="76" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="346" t="s">
+      <c r="D75" s="341"/>
+      <c r="E75" s="341"/>
+      <c r="F75" s="341"/>
+      <c r="G75" s="341"/>
+      <c r="H75" s="341"/>
+      <c r="I75" s="341"/>
+      <c r="J75" s="341"/>
+    </row>
+    <row r="76" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A76" s="344" t="s">
         <v>57</v>
       </c>
-      <c r="B76" s="346"/>
-      <c r="C76" s="340" t="s">
+      <c r="B76" s="344"/>
+      <c r="C76" s="341" t="s">
         <v>753</v>
       </c>
-      <c r="D76" s="340"/>
-      <c r="E76" s="340"/>
-      <c r="F76" s="340"/>
-      <c r="G76" s="340"/>
-      <c r="H76" s="340"/>
-      <c r="I76" s="340"/>
-      <c r="J76" s="340"/>
-    </row>
-    <row r="77" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="346" t="s">
+      <c r="D76" s="341"/>
+      <c r="E76" s="341"/>
+      <c r="F76" s="341"/>
+      <c r="G76" s="341"/>
+      <c r="H76" s="341"/>
+      <c r="I76" s="341"/>
+      <c r="J76" s="341"/>
+    </row>
+    <row r="77" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A77" s="344" t="s">
         <v>754</v>
       </c>
-      <c r="B77" s="346"/>
-      <c r="C77" s="340" t="s">
+      <c r="B77" s="344"/>
+      <c r="C77" s="341" t="s">
         <v>755</v>
       </c>
-      <c r="D77" s="340"/>
-      <c r="E77" s="340"/>
-      <c r="F77" s="340"/>
-      <c r="G77" s="340"/>
-      <c r="H77" s="340"/>
-      <c r="I77" s="340"/>
-      <c r="J77" s="340"/>
-    </row>
-    <row r="78" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="346" t="s">
+      <c r="D77" s="341"/>
+      <c r="E77" s="341"/>
+      <c r="F77" s="341"/>
+      <c r="G77" s="341"/>
+      <c r="H77" s="341"/>
+      <c r="I77" s="341"/>
+      <c r="J77" s="341"/>
+    </row>
+    <row r="78" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A78" s="344" t="s">
         <v>756</v>
       </c>
-      <c r="B78" s="346"/>
-      <c r="C78" s="340" t="s">
+      <c r="B78" s="344"/>
+      <c r="C78" s="341" t="s">
         <v>757</v>
       </c>
-      <c r="D78" s="340"/>
-      <c r="E78" s="340"/>
-      <c r="F78" s="340"/>
-      <c r="G78" s="340"/>
-      <c r="H78" s="340"/>
-      <c r="I78" s="340"/>
-      <c r="J78" s="340"/>
-    </row>
-    <row r="79" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="346" t="s">
+      <c r="D78" s="341"/>
+      <c r="E78" s="341"/>
+      <c r="F78" s="341"/>
+      <c r="G78" s="341"/>
+      <c r="H78" s="341"/>
+      <c r="I78" s="341"/>
+      <c r="J78" s="341"/>
+    </row>
+    <row r="79" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A79" s="344" t="s">
         <v>758</v>
       </c>
-      <c r="B79" s="346"/>
-      <c r="C79" s="340" t="s">
+      <c r="B79" s="344"/>
+      <c r="C79" s="341" t="s">
         <v>759</v>
       </c>
-      <c r="D79" s="340"/>
-      <c r="E79" s="340"/>
-      <c r="F79" s="340"/>
-      <c r="G79" s="340"/>
-      <c r="H79" s="340"/>
-      <c r="I79" s="340"/>
-      <c r="J79" s="340"/>
-    </row>
-    <row r="80" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="347" t="s">
+      <c r="D79" s="341"/>
+      <c r="E79" s="341"/>
+      <c r="F79" s="341"/>
+      <c r="G79" s="341"/>
+      <c r="H79" s="341"/>
+      <c r="I79" s="341"/>
+      <c r="J79" s="341"/>
+    </row>
+    <row r="80" spans="1:10" ht="14.4" customHeight="1">
+      <c r="A80" s="349" t="s">
         <v>760</v>
       </c>
-      <c r="B80" s="347"/>
-      <c r="C80" s="341" t="s">
+      <c r="B80" s="349"/>
+      <c r="C80" s="343" t="s">
         <v>761</v>
       </c>
-      <c r="D80" s="341"/>
-      <c r="E80" s="341"/>
-      <c r="F80" s="341"/>
-      <c r="G80" s="341"/>
-      <c r="H80" s="341"/>
-      <c r="I80" s="341"/>
-      <c r="J80" s="341"/>
-    </row>
-    <row r="81" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="348" t="s">
+      <c r="D80" s="343"/>
+      <c r="E80" s="343"/>
+      <c r="F80" s="343"/>
+      <c r="G80" s="343"/>
+      <c r="H80" s="343"/>
+      <c r="I80" s="343"/>
+      <c r="J80" s="343"/>
+    </row>
+    <row r="81" spans="1:10" ht="14.4" customHeight="1"/>
+    <row r="82" spans="1:10" ht="21.6" customHeight="1">
+      <c r="A82" s="342" t="s">
         <v>762</v>
       </c>
-      <c r="B82" s="348"/>
-      <c r="C82" s="348"/>
-      <c r="D82" s="348"/>
-      <c r="E82" s="348"/>
-      <c r="F82" s="348"/>
-      <c r="G82" s="348"/>
-      <c r="H82" s="348"/>
-      <c r="I82" s="348"/>
-      <c r="J82" s="348"/>
+      <c r="B82" s="342"/>
+      <c r="C82" s="342"/>
+      <c r="D82" s="342"/>
+      <c r="E82" s="342"/>
+      <c r="F82" s="342"/>
+      <c r="G82" s="342"/>
+      <c r="H82" s="342"/>
+      <c r="I82" s="342"/>
+      <c r="J82" s="342"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="356" t="s">
+        <v>791</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G78:J78"/>
+    <mergeCell ref="G79:J79"/>
+    <mergeCell ref="G80:J80"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C74:F74"/>
+    <mergeCell ref="C75:F75"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="C77:F77"/>
+    <mergeCell ref="C78:F78"/>
+    <mergeCell ref="C79:F79"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="G77:J77"/>
     <mergeCell ref="C70:F70"/>
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="C72:F72"/>
@@ -24838,26 +24874,6 @@
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="G77:J77"/>
-    <mergeCell ref="G78:J78"/>
-    <mergeCell ref="G79:J79"/>
-    <mergeCell ref="G80:J80"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C74:F74"/>
-    <mergeCell ref="C75:F75"/>
-    <mergeCell ref="C76:F76"/>
-    <mergeCell ref="C77:F77"/>
-    <mergeCell ref="C78:F78"/>
-    <mergeCell ref="C79:F79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24869,29 +24885,29 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="24" width="11.109375" style="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="325" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="325" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24">
       <c r="A5" s="4" t="s">
         <v>427</v>
       </c>
@@ -24919,7 +24935,7 @@
       <c r="W5" s="90"/>
       <c r="X5" s="90"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24">
       <c r="A6" s="216" t="s">
         <v>428</v>
       </c>
@@ -24989,7 +25005,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="216"/>
       <c r="B7" s="216"/>
       <c r="C7" s="217" t="s">
@@ -25049,7 +25065,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>454</v>
       </c>
@@ -25124,7 +25140,7 @@
         <v>0.47420050147362858</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>456</v>
       </c>
@@ -25199,7 +25215,7 @@
         <v>0.56329562286671098</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>458</v>
       </c>
@@ -25274,7 +25290,7 @@
         <v>2.5067864427403763</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>460</v>
       </c>
@@ -25349,7 +25365,7 @@
         <v>2.3974592788758033</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>462</v>
       </c>
@@ -25424,7 +25440,7 @@
         <v>0.84742075399639916</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>464</v>
       </c>
@@ -25499,7 +25515,7 @@
         <v>0.2458542229078288</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>466</v>
       </c>
@@ -25574,7 +25590,7 @@
         <v>0.30453172205438067</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>468</v>
       </c>
@@ -25649,14 +25665,14 @@
         <v>0.32999729510413855</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="F16"/>
       <c r="J16"/>
       <c r="M16" s="63"/>
       <c r="N16" s="63"/>
       <c r="O16"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="A17" s="1" t="s">
         <v>470</v>
       </c>
@@ -25742,7 +25758,7 @@
         <v>0.2458542229078288</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="A18" s="1" t="s">
         <v>471</v>
       </c>
@@ -25828,7 +25844,7 @@
         <v>0.32363090184169907</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
         <v>472</v>
       </c>
@@ -25914,7 +25930,7 @@
         <v>0.51874806217016978</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" s="1" t="s">
         <v>473</v>
       </c>
@@ -26000,7 +26016,7 @@
         <v>0.95869323000240825</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>474</v>
       </c>
@@ -26086,7 +26102,7 @@
         <v>1.2349303852162503</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>475</v>
       </c>
@@ -26172,12 +26188,12 @@
         <v>2.5067864427403763</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="F23"/>
       <c r="J23"/>
       <c r="O23"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="A24" s="4" t="s">
         <v>573</v>
       </c>
@@ -26205,7 +26221,7 @@
       <c r="W24" s="90"/>
       <c r="X24" s="90"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="A25" s="216" t="s">
         <v>428</v>
       </c>
@@ -26275,7 +26291,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="A26" s="216"/>
       <c r="B26" s="216"/>
       <c r="C26" s="217" t="s">
@@ -26335,7 +26351,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>476</v>
       </c>
@@ -26410,7 +26426,7 @@
         <v>0.45730318802862718</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>478</v>
       </c>
@@ -26485,7 +26501,7 @@
         <v>0.74579898541534562</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>480</v>
       </c>
@@ -26560,7 +26576,7 @@
         <v>0.3571725375389555</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>482</v>
       </c>
@@ -26635,7 +26651,7 @@
         <v>0.37714285714285717</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>484</v>
       </c>
@@ -26710,7 +26726,7 @@
         <v>0.78804213135068146</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>486</v>
       </c>
@@ -26785,7 +26801,7 @@
         <v>0.50961887477313972</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>488</v>
       </c>
@@ -26860,7 +26876,7 @@
         <v>0.45774647887323949</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>490</v>
       </c>
@@ -26935,14 +26951,14 @@
         <v>0.69504778453518679</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="F35"/>
       <c r="J35"/>
       <c r="M35" s="63"/>
       <c r="N35" s="63"/>
       <c r="O35"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>470</v>
       </c>
@@ -27028,7 +27044,7 @@
         <v>0.3571725375389555</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
         <v>471</v>
       </c>
@@ -27114,7 +27130,7 @@
         <v>0.43726310530718471</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
         <v>472</v>
       </c>
@@ -27200,7 +27216,7 @@
         <v>0.48368267682318961</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" s="1" t="s">
         <v>473</v>
       </c>
@@ -27286,7 +27302,7 @@
         <v>0.54848410470725417</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>474</v>
       </c>
@@ -27372,7 +27388,7 @@
         <v>0.70773558475522647</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24">
       <c r="A41" s="1" t="s">
         <v>475</v>
       </c>
@@ -27458,12 +27474,12 @@
         <v>0.78804213135068146</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24">
       <c r="F42"/>
       <c r="J42"/>
       <c r="O42"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24">
       <c r="A43" s="4" t="s">
         <v>574</v>
       </c>
@@ -27491,7 +27507,7 @@
       <c r="W43" s="90"/>
       <c r="X43" s="90"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24">
       <c r="A44" s="216" t="s">
         <v>428</v>
       </c>
@@ -27561,7 +27577,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24">
       <c r="A45" s="216"/>
       <c r="B45" s="216"/>
       <c r="C45" s="217" t="s">
@@ -27621,7 +27637,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24">
       <c r="A46" t="s">
         <v>492</v>
       </c>
@@ -27696,7 +27712,7 @@
         <v>6.3040345821325658E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24">
       <c r="A47" t="s">
         <v>494</v>
       </c>
@@ -27771,7 +27787,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24">
       <c r="A48" t="s">
         <v>496</v>
       </c>
@@ -27846,7 +27862,7 @@
         <v>0.24158130139950945</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>498</v>
       </c>
@@ -27921,7 +27937,7 @@
         <v>0.1194169947592105</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>500</v>
       </c>
@@ -27996,7 +28012,7 @@
         <v>0.24099247405910706</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>502</v>
       </c>
@@ -28071,7 +28087,7 @@
         <v>0.18666666666666665</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>504</v>
       </c>
@@ -28146,7 +28162,7 @@
         <v>0.13672608454648888</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>506</v>
       </c>
@@ -28221,14 +28237,14 @@
         <v>0.32653061224489793</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24">
       <c r="F54"/>
       <c r="J54"/>
       <c r="M54" s="63"/>
       <c r="N54" s="63"/>
       <c r="O54"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24">
       <c r="A55" s="1" t="s">
         <v>470</v>
       </c>
@@ -28314,7 +28330,7 @@
         <v>6.3040345821325658E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24">
       <c r="A56" s="1" t="s">
         <v>471</v>
       </c>
@@ -28399,7 +28415,7 @@
         <v>0.13239881209966928</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24">
       <c r="A57" s="1" t="s">
         <v>472</v>
       </c>
@@ -28484,7 +28500,7 @@
         <v>0.20833333333333331</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24">
       <c r="A58" s="1" t="s">
         <v>473</v>
       </c>
@@ -28569,7 +28585,7 @@
         <v>0.19311930993715076</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24">
       <c r="A59" s="1" t="s">
         <v>474</v>
       </c>
@@ -28654,7 +28670,7 @@
         <v>0.24113968089420768</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24">
       <c r="A60" s="1" t="s">
         <v>475</v>
       </c>
@@ -28754,19 +28770,19 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="325" t="s">
         <v>779</v>
       </c>
@@ -28778,7 +28794,7 @@
       <c r="G2" s="219"/>
       <c r="H2" s="219"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="325" t="s">
         <v>780</v>
       </c>
@@ -28790,7 +28806,7 @@
       <c r="G3" s="219"/>
       <c r="H3" s="219"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24">
       <c r="A5" s="4" t="s">
         <v>568</v>
       </c>
@@ -28818,7 +28834,7 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24">
       <c r="A6" s="216" t="s">
         <v>428</v>
       </c>
@@ -28888,7 +28904,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="216"/>
       <c r="B7" s="216"/>
       <c r="C7" s="217" t="s">
@@ -28948,7 +28964,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>509</v>
       </c>
@@ -29024,7 +29040,7 @@
         <v>2.3060259775174012</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>511</v>
       </c>
@@ -29100,7 +29116,7 @@
         <v>1.3092121869826105</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>513</v>
       </c>
@@ -29176,7 +29192,7 @@
         <v>1.1272696404317679</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>515</v>
       </c>
@@ -29252,7 +29268,7 @@
         <v>2.4611143925969676</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>517</v>
       </c>
@@ -29328,7 +29344,7 @@
         <v>0.11569306279854508</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>519</v>
       </c>
@@ -29404,7 +29420,7 @@
         <v>1.9230769230769229</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>521</v>
       </c>
@@ -29480,7 +29496,7 @@
         <v>1.3955938199032409</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>523</v>
       </c>
@@ -29556,7 +29572,7 @@
         <v>2.9792100789987206</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="A16" t="s">
         <v>525</v>
       </c>
@@ -29632,7 +29648,7 @@
         <v>2.4652227504842403</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="C17" s="118"/>
       <c r="D17" s="118"/>
       <c r="E17" s="118"/>
@@ -29654,7 +29670,7 @@
       <c r="W17" s="54"/>
       <c r="X17" s="63"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="A18" s="1" t="s">
         <v>470</v>
       </c>
@@ -29741,7 +29757,7 @@
         <v>0.11569306279854508</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" s="1" t="s">
         <v>471</v>
       </c>
@@ -29828,7 +29844,7 @@
         <v>1.3092121869826105</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" s="1" t="s">
         <v>472</v>
       </c>
@@ -29915,7 +29931,7 @@
         <v>1.9230769230769229</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" s="1" t="s">
         <v>473</v>
       </c>
@@ -30002,7 +30018,7 @@
         <v>1.7869354258656018</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" s="1" t="s">
         <v>474</v>
       </c>
@@ -30089,7 +30105,7 @@
         <v>2.4611143925969676</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="A23" s="1" t="s">
         <v>475</v>
       </c>
@@ -30176,7 +30192,7 @@
         <v>2.9792100789987206</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="C24" s="54"/>
       <c r="D24" s="54"/>
       <c r="E24" s="54"/>
@@ -30198,7 +30214,7 @@
       <c r="W24" s="54"/>
       <c r="X24" s="54"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="C25" s="54"/>
       <c r="D25" s="54"/>
       <c r="E25" s="54"/>
@@ -30220,7 +30236,7 @@
       <c r="W25" s="54"/>
       <c r="X25" s="54"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="A26" s="4" t="s">
         <v>569</v>
       </c>
@@ -30248,7 +30264,7 @@
       <c r="W26" s="90"/>
       <c r="X26" s="90"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="A27" s="216" t="s">
         <v>428</v>
       </c>
@@ -30318,7 +30334,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" s="216"/>
       <c r="B28" s="216"/>
       <c r="C28" s="217" t="s">
@@ -30378,7 +30394,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>527</v>
       </c>
@@ -30454,7 +30470,7 @@
         <v>0.97631992779118137</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>529</v>
       </c>
@@ -30530,7 +30546,7 @@
         <v>0.26644721773217195</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>531</v>
       </c>
@@ -30606,7 +30622,7 @@
         <v>0.17631938396261609</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>533</v>
       </c>
@@ -30682,7 +30698,7 @@
         <v>0.45129188262268549</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>535</v>
       </c>
@@ -30758,7 +30774,7 @@
         <v>4.3509577509172351E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="C34" s="118"/>
       <c r="D34" s="118"/>
       <c r="E34" s="118"/>
@@ -30780,7 +30796,7 @@
       <c r="W34" s="54"/>
       <c r="X34" s="63"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="A35" s="1" t="s">
         <v>470</v>
       </c>
@@ -30867,7 +30883,7 @@
         <v>4.3509577509172351E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="A36" s="1" t="s">
         <v>471</v>
       </c>
@@ -30954,7 +30970,7 @@
         <v>0.17631938396261609</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="1" t="s">
         <v>472</v>
       </c>
@@ -31041,7 +31057,7 @@
         <v>0.26644721773217195</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="1" t="s">
         <v>473</v>
       </c>
@@ -31128,7 +31144,7 @@
         <v>0.38277759792356542</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" s="1" t="s">
         <v>474</v>
       </c>
@@ -31215,7 +31231,7 @@
         <v>0.45129188262268549</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" s="1" t="s">
         <v>475</v>
       </c>
@@ -31314,29 +31330,29 @@
     <tabColor rgb="FFED7D31"/>
   </sheetPr>
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="219" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="219" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24">
       <c r="A5" s="4" t="s">
         <v>570</v>
       </c>
@@ -31364,7 +31380,7 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24">
       <c r="A6" s="216" t="s">
         <v>428</v>
       </c>
@@ -31434,7 +31450,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="216"/>
       <c r="B7" s="216"/>
       <c r="C7" s="217" t="s">
@@ -31494,7 +31510,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>539</v>
       </c>
@@ -31570,7 +31586,7 @@
         <v>1.1995170504033592</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>541</v>
       </c>
@@ -31646,7 +31662,7 @@
         <v>2.5351657235246563</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="C10" s="54"/>
       <c r="D10" s="54"/>
       <c r="E10" s="54"/>
@@ -31668,7 +31684,7 @@
       <c r="W10" s="54"/>
       <c r="X10" s="54"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" s="1" t="s">
         <v>470</v>
       </c>
@@ -31755,7 +31771,7 @@
         <v>1.1995170504033592</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" s="1" t="s">
         <v>471</v>
       </c>
@@ -31842,7 +31858,7 @@
         <v>1.5334292186836835</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" s="1" t="s">
         <v>472</v>
       </c>
@@ -31929,7 +31945,7 @@
         <v>1.8673413869640076</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" s="1" t="s">
         <v>473</v>
       </c>
@@ -32016,7 +32032,7 @@
         <v>1.8673413869640076</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" s="1" t="s">
         <v>474</v>
       </c>
@@ -32103,7 +32119,7 @@
         <v>2.2012535552443317</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="A16" s="1" t="s">
         <v>475</v>
       </c>
@@ -32190,7 +32206,7 @@
         <v>2.5351657235246563</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="C17" s="54"/>
       <c r="D17" s="54"/>
       <c r="E17" s="54"/>
@@ -32212,7 +32228,7 @@
       <c r="W17" s="54"/>
       <c r="X17" s="54"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="C18" s="54"/>
       <c r="D18" s="54"/>
       <c r="E18" s="54"/>
@@ -32234,7 +32250,7 @@
       <c r="W18" s="54"/>
       <c r="X18" s="54"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" s="4" t="s">
         <v>571</v>
       </c>
@@ -32266,7 +32282,7 @@
       <c r="W19" s="90"/>
       <c r="X19" s="90"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" s="216" t="s">
         <v>428</v>
       </c>
@@ -32336,7 +32352,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" s="216"/>
       <c r="B21" s="216"/>
       <c r="C21" s="217" t="s">
@@ -32396,7 +32412,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>543</v>
       </c>
@@ -32471,7 +32487,7 @@
         <v>1.2475687691025283</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>545</v>
       </c>
@@ -32546,7 +32562,7 @@
         <v>3.4963718868279625</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>547</v>
       </c>
@@ -32621,7 +32637,7 @@
         <v>6.2090435588369361</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>549</v>
       </c>
@@ -32696,7 +32712,7 @@
         <v>3.1307916335716173</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>551</v>
       </c>
@@ -32771,7 +32787,7 @@
         <v>2.7863640490240584</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="C27" s="54"/>
       <c r="D27" s="54"/>
       <c r="E27" s="54"/>
@@ -32793,7 +32809,7 @@
       <c r="W27" s="54"/>
       <c r="X27" s="54"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" s="1" t="s">
         <v>470</v>
       </c>
@@ -32880,7 +32896,7 @@
         <v>1.2475687691025283</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" s="1" t="s">
         <v>471</v>
       </c>
@@ -32967,7 +32983,7 @@
         <v>2.7863640490240584</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" s="1" t="s">
         <v>472</v>
       </c>
@@ -33054,7 +33070,7 @@
         <v>3.1307916335716173</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" s="1" t="s">
         <v>473</v>
       </c>
@@ -33141,7 +33157,7 @@
         <v>3.3740279794726207</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" s="1" t="s">
         <v>474</v>
       </c>
@@ -33228,7 +33244,7 @@
         <v>3.4963718868279625</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" s="1" t="s">
         <v>475</v>
       </c>
@@ -33315,7 +33331,7 @@
         <v>6.2090435588369361</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="C34" s="54"/>
       <c r="D34" s="54"/>
       <c r="E34" s="117"/>
@@ -33337,7 +33353,7 @@
       <c r="W34" s="64"/>
       <c r="X34" s="63"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="C35" s="54"/>
       <c r="D35" s="54"/>
       <c r="E35" s="54"/>
@@ -33359,7 +33375,7 @@
       <c r="W35" s="54"/>
       <c r="X35" s="54"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="A36" s="4" t="s">
         <v>572</v>
       </c>
@@ -33391,7 +33407,7 @@
       <c r="W36" s="90"/>
       <c r="X36" s="90"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="216" t="s">
         <v>428</v>
       </c>
@@ -33461,7 +33477,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="216"/>
       <c r="B38" s="216"/>
       <c r="C38" s="217" t="s">
@@ -33521,7 +33537,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>553</v>
       </c>
@@ -33596,7 +33612,7 @@
         <v>0.81237483229958585</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>555</v>
       </c>
@@ -33671,7 +33687,7 @@
         <v>0.9038447507334364</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>557</v>
       </c>
@@ -33746,7 +33762,7 @@
         <v>0.79969661227393107</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>784</v>
       </c>
@@ -33821,7 +33837,7 @@
         <v>1.1818340278166037</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>559</v>
       </c>
@@ -33896,7 +33912,7 @@
         <v>0.99384615384615393</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24">
       <c r="C44" s="54"/>
       <c r="D44" s="54"/>
       <c r="E44" s="54"/>
@@ -33918,7 +33934,7 @@
       <c r="W44" s="54"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24">
       <c r="A45" s="1" t="s">
         <v>470</v>
       </c>
@@ -34005,7 +34021,7 @@
         <v>0.79969661227393107</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24">
       <c r="A46" s="1" t="s">
         <v>471</v>
       </c>
@@ -34092,7 +34108,7 @@
         <v>0.81237483229958585</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24">
       <c r="A47" s="1" t="s">
         <v>472</v>
       </c>
@@ -34179,7 +34195,7 @@
         <v>0.9038447507334364</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24">
       <c r="A48" s="1" t="s">
         <v>473</v>
       </c>
@@ -34266,7 +34282,7 @@
         <v>0.93831927539394222</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24">
       <c r="A49" s="1" t="s">
         <v>474</v>
       </c>
@@ -34353,7 +34369,7 @@
         <v>0.99384615384615393</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24">
       <c r="A50" s="1" t="s">
         <v>475</v>
       </c>
@@ -34452,36 +34468,36 @@
     <tabColor rgb="FF548235"/>
   </sheetPr>
   <dimension ref="A1:H51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="8" width="11.109375" customWidth="1"/>
     <col min="9" max="18" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="325" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="350" t="s">
         <v>390</v>
       </c>
-      <c r="B4" s="351"/>
-      <c r="C4" s="351"/>
-      <c r="D4" s="351"/>
-      <c r="E4" s="351"/>
-      <c r="F4" s="351"/>
-      <c r="G4" s="351"/>
-      <c r="H4" s="351"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="352"/>
+      <c r="C4" s="352"/>
+      <c r="D4" s="352"/>
+      <c r="E4" s="352"/>
+      <c r="F4" s="352"/>
+      <c r="G4" s="352"/>
+      <c r="H4" s="352"/>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="80" t="s">
         <v>391</v>
       </c>
@@ -34505,7 +34521,7 @@
       </c>
       <c r="H5" s="34"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>222</v>
       </c>
@@ -34531,7 +34547,7 @@
         <v>40380.417792</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>223</v>
       </c>
@@ -34557,7 +34573,7 @@
         <v>26135.624592</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>224</v>
       </c>
@@ -34583,7 +34599,7 @@
         <v>6046.1359200000006</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>225</v>
       </c>
@@ -34609,7 +34625,7 @@
         <v>8198.6572799999976</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>388</v>
       </c>
@@ -34635,7 +34651,7 @@
         <v>17249.51223072</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -34661,7 +34677,7 @@
         <v>1451.0726208000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>381</v>
       </c>
@@ -34687,7 +34703,7 @@
         <v>983.83887359999972</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>382</v>
       </c>
@@ -34713,7 +34729,7 @@
         <v>11750.570369999998</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>230</v>
       </c>
@@ -34739,7 +34755,7 @@
         <v>-24094.151516159996</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>231</v>
       </c>
@@ -34762,7 +34778,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -34770,7 +34786,7 @@
       <c r="F16" s="54"/>
       <c r="G16" s="54"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="355" t="s">
         <v>392</v>
       </c>
@@ -34782,7 +34798,7 @@
       <c r="G18" s="355"/>
       <c r="H18" s="355"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="6" t="s">
         <v>391</v>
       </c>
@@ -34804,7 +34820,7 @@
       <c r="G19" s="52"/>
       <c r="H19" s="52"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>222</v>
       </c>
@@ -34830,7 +34846,7 @@
       <c r="G20" s="54"/>
       <c r="H20" s="54"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>223</v>
       </c>
@@ -34856,7 +34872,7 @@
       <c r="G21" s="54"/>
       <c r="H21" s="54"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>224</v>
       </c>
@@ -34882,7 +34898,7 @@
       <c r="G22" s="54"/>
       <c r="H22" s="54"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>225</v>
       </c>
@@ -34908,7 +34924,7 @@
       <c r="G23" s="54"/>
       <c r="H23" s="54"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="325" t="s">
         <v>782</v>
       </c>
@@ -34922,7 +34938,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="355" t="s">
         <v>397</v>
       </c>
@@ -34934,7 +34950,7 @@
       <c r="G26" s="355"/>
       <c r="H26" s="355"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="6" t="s">
         <v>398</v>
       </c>
@@ -34954,7 +34970,7 @@
       <c r="G27" s="52"/>
       <c r="H27" s="52"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>222</v>
       </c>
@@ -34974,7 +34990,7 @@
       <c r="G28" s="54"/>
       <c r="H28" s="54"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>401</v>
       </c>
@@ -34995,7 +35011,7 @@
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>378</v>
       </c>
@@ -35016,7 +35032,7 @@
       <c r="G30" s="54"/>
       <c r="H30" s="54"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>379</v>
       </c>
@@ -35037,7 +35053,7 @@
       <c r="G31" s="54"/>
       <c r="H31" s="54"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>388</v>
       </c>
@@ -35058,7 +35074,7 @@
       <c r="G32" s="54"/>
       <c r="H32" s="54"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>380</v>
       </c>
@@ -35079,7 +35095,7 @@
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>381</v>
       </c>
@@ -35100,7 +35116,7 @@
       <c r="G34" s="54"/>
       <c r="H34" s="54"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -35121,7 +35137,7 @@
       <c r="G35" s="54"/>
       <c r="H35" s="54"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>414</v>
       </c>
@@ -35142,7 +35158,7 @@
       <c r="G36" s="54"/>
       <c r="H36" s="54"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="355" t="s">
         <v>402</v>
       </c>
@@ -35154,7 +35170,7 @@
       <c r="G38" s="355"/>
       <c r="H38" s="355"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="6" t="s">
         <v>403</v>
       </c>
@@ -35174,7 +35190,7 @@
       <c r="G39" s="52"/>
       <c r="H39" s="52"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>222</v>
       </c>
@@ -35195,7 +35211,7 @@
       <c r="G40" s="54"/>
       <c r="H40" s="54"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>401</v>
       </c>
@@ -35216,7 +35232,7 @@
       <c r="G41" s="54"/>
       <c r="H41" s="54"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>378</v>
       </c>
@@ -35237,7 +35253,7 @@
       <c r="G42" s="54"/>
       <c r="H42" s="54"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>379</v>
       </c>
@@ -35258,7 +35274,7 @@
       <c r="G43" s="54"/>
       <c r="H43" s="54"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
         <v>405</v>
       </c>
@@ -35270,27 +35286,27 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="157" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="157" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1">
       <c r="A49" s="157" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:1">
       <c r="A50" s="157" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1">
       <c r="A51" s="157" t="s">
         <v>410</v>
       </c>
@@ -35313,28 +35329,28 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:F161"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="46.33203125" customWidth="1"/>
     <col min="2" max="6" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="325" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="325" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="232" t="s">
         <v>383</v>
       </c>
@@ -35351,7 +35367,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
         <v>588</v>
       </c>
@@ -35361,7 +35377,7 @@
       <c r="E6" s="234"/>
       <c r="F6" s="234"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>87</v>
       </c>
@@ -35381,7 +35397,7 @@
         <v>4694</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>589</v>
       </c>
@@ -35401,7 +35417,7 @@
         <v>-2388</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>590</v>
       </c>
@@ -35426,7 +35442,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>591</v>
       </c>
@@ -35451,7 +35467,7 @@
         <v>0.49126544524925436</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>592</v>
       </c>
@@ -35471,7 +35487,7 @@
         <v>-3514</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>593</v>
       </c>
@@ -35491,7 +35507,7 @@
         <v>-746</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>594</v>
       </c>
@@ -35511,7 +35527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>595</v>
       </c>
@@ -35531,7 +35547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
         <v>596</v>
       </c>
@@ -35556,14 +35572,14 @@
         <v>-6637</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
       <c r="E16" s="54"/>
       <c r="F16" s="54"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>597</v>
       </c>
@@ -35588,7 +35604,7 @@
         <v>-1943</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>598</v>
       </c>
@@ -35613,7 +35629,7 @@
         <v>-0.41393268001704303</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>599</v>
       </c>
@@ -35633,7 +35649,7 @@
         <v>-664</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>600</v>
       </c>
@@ -35653,7 +35669,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>601</v>
       </c>
@@ -35673,7 +35689,7 @@
         <v>-1876</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>602</v>
       </c>
@@ -35698,7 +35714,7 @@
         <v>-4270</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>603</v>
       </c>
@@ -35718,7 +35734,7 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>604</v>
       </c>
@@ -35743,7 +35759,7 @@
         <v>-4276</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>605</v>
       </c>
@@ -35768,14 +35784,14 @@
         <v>-0.91095014912654448</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
       <c r="E26" s="54"/>
       <c r="F26" s="54"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="4" t="s">
         <v>606</v>
       </c>
@@ -35785,7 +35801,7 @@
       <c r="E27" s="234"/>
       <c r="F27" s="234"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>607</v>
       </c>
@@ -35805,7 +35821,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>608</v>
       </c>
@@ -35821,7 +35837,7 @@
       <c r="E29" s="54"/>
       <c r="F29" s="54"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>609</v>
       </c>
@@ -35837,7 +35853,7 @@
       <c r="E30" s="54"/>
       <c r="F30" s="54"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
         <v>610</v>
       </c>
@@ -35857,7 +35873,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>611</v>
       </c>
@@ -35873,7 +35889,7 @@
       <c r="E32" s="54"/>
       <c r="F32" s="54"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>612</v>
       </c>
@@ -35889,7 +35905,7 @@
       <c r="E33" s="54"/>
       <c r="F33" s="54"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
         <v>613</v>
       </c>
@@ -35909,7 +35925,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>614</v>
       </c>
@@ -35925,7 +35941,7 @@
       <c r="E35" s="54"/>
       <c r="F35" s="54"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>615</v>
       </c>
@@ -35941,7 +35957,7 @@
       <c r="E36" s="54"/>
       <c r="F36" s="54"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
         <v>616</v>
       </c>
@@ -35966,14 +35982,14 @@
         <v>4694</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="B38" s="54"/>
       <c r="C38" s="54"/>
       <c r="D38" s="54"/>
       <c r="E38" s="54"/>
       <c r="F38" s="54"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="4" t="s">
         <v>617</v>
       </c>
@@ -35983,7 +35999,7 @@
       <c r="E39" s="234"/>
       <c r="F39" s="234"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="231" t="s">
         <v>618</v>
       </c>
@@ -35993,7 +36009,7 @@
       <c r="E40" s="54"/>
       <c r="F40" s="54"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>619</v>
       </c>
@@ -36013,7 +36029,7 @@
         <v>-662</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>620</v>
       </c>
@@ -36033,7 +36049,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>621</v>
       </c>
@@ -36053,7 +36069,7 @@
         <v>-2469</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
         <v>622</v>
       </c>
@@ -36078,14 +36094,14 @@
         <v>-1943</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="B45" s="54"/>
       <c r="C45" s="54"/>
       <c r="D45" s="54"/>
       <c r="E45" s="54"/>
       <c r="F45" s="54"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="231" t="s">
         <v>623</v>
       </c>
@@ -36095,7 +36111,7 @@
       <c r="E46" s="54"/>
       <c r="F46" s="54"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>619</v>
       </c>
@@ -36115,7 +36131,7 @@
         <v>-351</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>620</v>
       </c>
@@ -36135,7 +36151,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>621</v>
       </c>
@@ -36155,7 +36171,7 @@
         <v>-609</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
         <v>624</v>
       </c>
@@ -36180,7 +36196,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
         <v>91</v>
       </c>
@@ -36205,14 +36221,14 @@
         <v>0.24009373668512995</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="B52" s="54"/>
       <c r="C52" s="54"/>
       <c r="D52" s="54"/>
       <c r="E52" s="54"/>
       <c r="F52" s="54"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" s="231" t="s">
         <v>625</v>
       </c>
@@ -36222,7 +36238,7 @@
       <c r="E53" s="54"/>
       <c r="F53" s="54"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>619</v>
       </c>
@@ -36238,7 +36254,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>620</v>
       </c>
@@ -36254,7 +36270,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>621</v>
       </c>
@@ -36270,7 +36286,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
         <v>626</v>
       </c>
@@ -36291,14 +36307,14 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="B58" s="54"/>
       <c r="C58" s="54"/>
       <c r="D58" s="54"/>
       <c r="E58" s="54"/>
       <c r="F58" s="54"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" s="231" t="s">
         <v>627</v>
       </c>
@@ -36308,7 +36324,7 @@
       <c r="E59" s="54"/>
       <c r="F59" s="54"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>619</v>
       </c>
@@ -36328,7 +36344,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>620</v>
       </c>
@@ -36348,7 +36364,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>621</v>
       </c>
@@ -36368,7 +36384,7 @@
         <v>7723</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" s="1" t="s">
         <v>628</v>
       </c>
@@ -36393,7 +36409,7 @@
         <v>10107</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>629</v>
       </c>
@@ -36418,14 +36434,14 @@
         <v>2.1531742650191732</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="B65" s="54"/>
       <c r="C65" s="54"/>
       <c r="D65" s="54"/>
       <c r="E65" s="54"/>
       <c r="F65" s="54"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" s="4" t="s">
         <v>630</v>
       </c>
@@ -36435,7 +36451,7 @@
       <c r="E66" s="234"/>
       <c r="F66" s="234"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>631</v>
       </c>
@@ -36451,7 +36467,7 @@
         <v>15852</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>632</v>
       </c>
@@ -36467,7 +36483,7 @@
         <v>29732</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>633</v>
       </c>
@@ -36483,7 +36499,7 @@
         <v>53879</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>634</v>
       </c>
@@ -36497,7 +36513,7 @@
       <c r="E70" s="54"/>
       <c r="F70" s="54"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" s="1" t="s">
         <v>635</v>
       </c>
@@ -36513,14 +36529,14 @@
         <v>102094</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="B72" s="54"/>
       <c r="C72" s="54"/>
       <c r="D72" s="54"/>
       <c r="E72" s="54"/>
       <c r="F72" s="54"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>636</v>
       </c>
@@ -36536,7 +36552,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>637</v>
       </c>
@@ -36552,7 +36568,7 @@
         <v>24436</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>638</v>
       </c>
@@ -36566,7 +36582,7 @@
       <c r="E75" s="54"/>
       <c r="F75" s="54"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
         <v>639</v>
       </c>
@@ -36582,7 +36598,7 @@
         <v>60512</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>640</v>
       </c>
@@ -36598,7 +36614,7 @@
         <v>7049</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
         <v>641</v>
       </c>
@@ -36614,7 +36630,7 @@
         <v>34533</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
         <v>642</v>
       </c>
@@ -36630,7 +36646,7 @@
       <c r="E79" s="54"/>
       <c r="F79" s="54"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
         <v>643</v>
       </c>
@@ -36646,14 +36662,14 @@
       <c r="E80" s="54"/>
       <c r="F80" s="54"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="B81" s="54"/>
       <c r="C81" s="54"/>
       <c r="D81" s="54"/>
       <c r="E81" s="54"/>
       <c r="F81" s="54"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" s="4" t="s">
         <v>644</v>
       </c>
@@ -36663,7 +36679,7 @@
       <c r="E82" s="234"/>
       <c r="F82" s="234"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" s="1" t="s">
         <v>645</v>
       </c>
@@ -36683,7 +36699,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
         <v>646</v>
       </c>
@@ -36703,7 +36719,7 @@
         <v>-10107</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" s="1" t="s">
         <v>647</v>
       </c>
@@ -36728,7 +36744,7 @@
         <v>-9060</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
         <v>648</v>
       </c>
@@ -36748,7 +36764,7 @@
         <v>-16724</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" s="1" t="s">
         <v>649</v>
       </c>
@@ -36768,14 +36784,14 @@
         <v>7125</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="B88" s="54"/>
       <c r="C88" s="54"/>
       <c r="D88" s="54"/>
       <c r="E88" s="54"/>
       <c r="F88" s="54"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" s="4" t="s">
         <v>650</v>
       </c>
@@ -36785,7 +36801,7 @@
       <c r="E89" s="234"/>
       <c r="F89" s="234"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
         <v>651</v>
       </c>
@@ -36805,7 +36821,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" s="1" t="s">
         <v>652</v>
       </c>
@@ -36825,7 +36841,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
         <v>653</v>
       </c>
@@ -36845,7 +36861,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" s="1" t="s">
         <v>654</v>
       </c>
@@ -36865,7 +36881,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
         <v>655</v>
       </c>
@@ -36885,14 +36901,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="B95" s="54"/>
       <c r="C95" s="54"/>
       <c r="D95" s="54"/>
       <c r="E95" s="54"/>
       <c r="F95" s="54"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" s="4" t="s">
         <v>656</v>
       </c>
@@ -36902,7 +36918,7 @@
       <c r="E96" s="234"/>
       <c r="F96" s="234"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" s="1" t="s">
         <v>657</v>
       </c>
@@ -36921,7 +36937,7 @@
         <v>0.15416769117285467</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
         <v>658</v>
       </c>
@@ -36940,7 +36956,7 @@
         <v>-0.284393063583815</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" s="1" t="s">
         <v>659</v>
       </c>
@@ -36959,7 +36975,7 @@
         <v>0.315959595959596</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
         <v>660</v>
       </c>
@@ -36978,7 +36994,7 @@
         <v>0.12517193947730409</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" s="1" t="s">
         <v>661</v>
       </c>
@@ -36997,7 +37013,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" s="1" t="s">
         <v>662</v>
       </c>
@@ -37016,7 +37032,7 @@
         <v>1.4413043478260867</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" s="1" t="s">
         <v>663</v>
       </c>
@@ -37035,14 +37051,14 @@
         <v>0.44016506189821181</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="B104" s="54"/>
       <c r="C104" s="54"/>
       <c r="D104" s="54"/>
       <c r="E104" s="54"/>
       <c r="F104" s="54"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" s="1" t="s">
         <v>664</v>
       </c>
@@ -37054,7 +37070,7 @@
       <c r="E105" s="54"/>
       <c r="F105" s="54"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" s="1" t="s">
         <v>665</v>
       </c>
@@ -37066,7 +37082,7 @@
       <c r="E106" s="54"/>
       <c r="F106" s="54"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" s="1" t="s">
         <v>666</v>
       </c>
@@ -37082,378 +37098,378 @@
       <c r="E107" s="54"/>
       <c r="F107" s="54"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="B108" s="54"/>
       <c r="C108" s="54"/>
       <c r="D108" s="54"/>
       <c r="E108" s="54"/>
       <c r="F108" s="54"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="B109" s="54"/>
       <c r="C109" s="54"/>
       <c r="D109" s="54"/>
       <c r="E109" s="54"/>
       <c r="F109" s="54"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="B110" s="54"/>
       <c r="C110" s="54"/>
       <c r="D110" s="54"/>
       <c r="E110" s="54"/>
       <c r="F110" s="54"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="B111" s="54"/>
       <c r="C111" s="54"/>
       <c r="D111" s="54"/>
       <c r="E111" s="54"/>
       <c r="F111" s="54"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="B112" s="54"/>
       <c r="C112" s="54"/>
       <c r="D112" s="54"/>
       <c r="E112" s="54"/>
       <c r="F112" s="54"/>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:6">
       <c r="B113" s="54"/>
       <c r="C113" s="54"/>
       <c r="D113" s="54"/>
       <c r="E113" s="54"/>
       <c r="F113" s="54"/>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:6">
       <c r="B114" s="54"/>
       <c r="C114" s="54"/>
       <c r="D114" s="54"/>
       <c r="E114" s="54"/>
       <c r="F114" s="54"/>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:6">
       <c r="B115" s="54"/>
       <c r="C115" s="54"/>
       <c r="D115" s="54"/>
       <c r="E115" s="54"/>
       <c r="F115" s="54"/>
     </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:6">
       <c r="B116" s="54"/>
       <c r="C116" s="54"/>
       <c r="D116" s="54"/>
       <c r="E116" s="54"/>
       <c r="F116" s="54"/>
     </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:6">
       <c r="B117" s="54"/>
       <c r="C117" s="54"/>
       <c r="D117" s="54"/>
       <c r="E117" s="54"/>
       <c r="F117" s="54"/>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:6">
       <c r="B118" s="54"/>
       <c r="C118" s="54"/>
       <c r="D118" s="54"/>
       <c r="E118" s="54"/>
       <c r="F118" s="54"/>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:6">
       <c r="B119" s="54"/>
       <c r="C119" s="54"/>
       <c r="D119" s="54"/>
       <c r="E119" s="54"/>
       <c r="F119" s="54"/>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:6">
       <c r="B120" s="54"/>
       <c r="C120" s="54"/>
       <c r="D120" s="54"/>
       <c r="E120" s="54"/>
       <c r="F120" s="54"/>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:6">
       <c r="B121" s="54"/>
       <c r="C121" s="54"/>
       <c r="D121" s="54"/>
       <c r="E121" s="54"/>
       <c r="F121" s="54"/>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:6">
       <c r="B122" s="54"/>
       <c r="C122" s="54"/>
       <c r="D122" s="54"/>
       <c r="E122" s="54"/>
       <c r="F122" s="54"/>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:6">
       <c r="B123" s="54"/>
       <c r="C123" s="54"/>
       <c r="D123" s="54"/>
       <c r="E123" s="54"/>
       <c r="F123" s="54"/>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:6">
       <c r="B124" s="54"/>
       <c r="C124" s="54"/>
       <c r="D124" s="54"/>
       <c r="E124" s="54"/>
       <c r="F124" s="54"/>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:6">
       <c r="B125" s="54"/>
       <c r="C125" s="54"/>
       <c r="D125" s="54"/>
       <c r="E125" s="54"/>
       <c r="F125" s="54"/>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:6">
       <c r="B126" s="54"/>
       <c r="C126" s="54"/>
       <c r="D126" s="54"/>
       <c r="E126" s="54"/>
       <c r="F126" s="54"/>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:6">
       <c r="B127" s="54"/>
       <c r="C127" s="54"/>
       <c r="D127" s="54"/>
       <c r="E127" s="54"/>
       <c r="F127" s="54"/>
     </row>
-    <row r="128" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:6">
       <c r="B128" s="54"/>
       <c r="C128" s="54"/>
       <c r="D128" s="54"/>
       <c r="E128" s="54"/>
       <c r="F128" s="54"/>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:6">
       <c r="B129" s="54"/>
       <c r="C129" s="54"/>
       <c r="D129" s="54"/>
       <c r="E129" s="54"/>
       <c r="F129" s="54"/>
     </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:6">
       <c r="B130" s="54"/>
       <c r="C130" s="54"/>
       <c r="D130" s="54"/>
       <c r="E130" s="54"/>
       <c r="F130" s="54"/>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:6">
       <c r="B131" s="54"/>
       <c r="C131" s="54"/>
       <c r="D131" s="54"/>
       <c r="E131" s="54"/>
       <c r="F131" s="54"/>
     </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:6">
       <c r="B132" s="54"/>
       <c r="C132" s="54"/>
       <c r="D132" s="54"/>
       <c r="E132" s="54"/>
       <c r="F132" s="54"/>
     </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:6">
       <c r="B133" s="54"/>
       <c r="C133" s="54"/>
       <c r="D133" s="54"/>
       <c r="E133" s="54"/>
       <c r="F133" s="54"/>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:6">
       <c r="B134" s="54"/>
       <c r="C134" s="54"/>
       <c r="D134" s="54"/>
       <c r="E134" s="54"/>
       <c r="F134" s="54"/>
     </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:6">
       <c r="B135" s="54"/>
       <c r="C135" s="54"/>
       <c r="D135" s="54"/>
       <c r="E135" s="54"/>
       <c r="F135" s="54"/>
     </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:6">
       <c r="B136" s="54"/>
       <c r="C136" s="54"/>
       <c r="D136" s="54"/>
       <c r="E136" s="54"/>
       <c r="F136" s="54"/>
     </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:6">
       <c r="B137" s="54"/>
       <c r="C137" s="54"/>
       <c r="D137" s="54"/>
       <c r="E137" s="54"/>
       <c r="F137" s="54"/>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:6">
       <c r="B138" s="54"/>
       <c r="C138" s="54"/>
       <c r="D138" s="54"/>
       <c r="E138" s="54"/>
       <c r="F138" s="54"/>
     </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:6">
       <c r="B139" s="54"/>
       <c r="C139" s="54"/>
       <c r="D139" s="54"/>
       <c r="E139" s="54"/>
       <c r="F139" s="54"/>
     </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:6">
       <c r="B140" s="54"/>
       <c r="C140" s="54"/>
       <c r="D140" s="54"/>
       <c r="E140" s="54"/>
       <c r="F140" s="54"/>
     </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:6">
       <c r="B141" s="54"/>
       <c r="C141" s="54"/>
       <c r="D141" s="54"/>
       <c r="E141" s="54"/>
       <c r="F141" s="54"/>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:6">
       <c r="B142" s="54"/>
       <c r="C142" s="54"/>
       <c r="D142" s="54"/>
       <c r="E142" s="54"/>
       <c r="F142" s="54"/>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:6">
       <c r="B143" s="54"/>
       <c r="C143" s="54"/>
       <c r="D143" s="54"/>
       <c r="E143" s="54"/>
       <c r="F143" s="54"/>
     </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:6">
       <c r="B144" s="54"/>
       <c r="C144" s="54"/>
       <c r="D144" s="54"/>
       <c r="E144" s="54"/>
       <c r="F144" s="54"/>
     </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:6">
       <c r="B145" s="54"/>
       <c r="C145" s="54"/>
       <c r="D145" s="54"/>
       <c r="E145" s="54"/>
       <c r="F145" s="54"/>
     </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:6">
       <c r="B146" s="54"/>
       <c r="C146" s="54"/>
       <c r="D146" s="54"/>
       <c r="E146" s="54"/>
       <c r="F146" s="54"/>
     </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:6">
       <c r="B147" s="54"/>
       <c r="C147" s="54"/>
       <c r="D147" s="54"/>
       <c r="E147" s="54"/>
       <c r="F147" s="54"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:6">
       <c r="B148" s="54"/>
       <c r="C148" s="54"/>
       <c r="D148" s="54"/>
       <c r="E148" s="54"/>
       <c r="F148" s="54"/>
     </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:6">
       <c r="B149" s="54"/>
       <c r="C149" s="54"/>
       <c r="D149" s="54"/>
       <c r="E149" s="54"/>
       <c r="F149" s="54"/>
     </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:6">
       <c r="B150" s="54"/>
       <c r="C150" s="54"/>
       <c r="D150" s="54"/>
       <c r="E150" s="54"/>
       <c r="F150" s="54"/>
     </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:6">
       <c r="B151" s="54"/>
       <c r="C151" s="54"/>
       <c r="D151" s="54"/>
       <c r="E151" s="54"/>
       <c r="F151" s="54"/>
     </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:6">
       <c r="B152" s="54"/>
       <c r="C152" s="54"/>
       <c r="D152" s="54"/>
       <c r="E152" s="54"/>
       <c r="F152" s="54"/>
     </row>
-    <row r="153" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:6">
       <c r="B153" s="54"/>
       <c r="C153" s="54"/>
       <c r="D153" s="54"/>
       <c r="E153" s="54"/>
       <c r="F153" s="54"/>
     </row>
-    <row r="154" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:6">
       <c r="B154" s="54"/>
       <c r="C154" s="54"/>
       <c r="D154" s="54"/>
       <c r="E154" s="54"/>
       <c r="F154" s="54"/>
     </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:6">
       <c r="B155" s="54"/>
       <c r="C155" s="54"/>
       <c r="D155" s="54"/>
       <c r="E155" s="54"/>
       <c r="F155" s="54"/>
     </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:6">
       <c r="B156" s="54"/>
       <c r="C156" s="54"/>
       <c r="D156" s="54"/>
       <c r="E156" s="54"/>
       <c r="F156" s="54"/>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:6">
       <c r="B157" s="54"/>
       <c r="C157" s="54"/>
       <c r="D157" s="54"/>
       <c r="E157" s="54"/>
       <c r="F157" s="54"/>
     </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:6">
       <c r="B158" s="54"/>
       <c r="C158" s="54"/>
       <c r="D158" s="54"/>
       <c r="E158" s="54"/>
       <c r="F158" s="54"/>
     </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:6">
       <c r="B159" s="54"/>
       <c r="C159" s="54"/>
       <c r="D159" s="54"/>
       <c r="E159" s="54"/>
       <c r="F159" s="54"/>
     </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:6">
       <c r="B160" s="54"/>
       <c r="C160" s="54"/>
       <c r="D160" s="54"/>
       <c r="E160" s="54"/>
       <c r="F160" s="54"/>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6">
       <c r="B161" s="54"/>
       <c r="C161" s="54"/>
       <c r="D161" s="54"/>
@@ -37472,87 +37488,87 @@
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
   <dimension ref="A1:J70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="51.88671875" customWidth="1"/>
     <col min="2" max="10" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="342" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="345" t="s">
         <v>764</v>
       </c>
-      <c r="B1" s="343"/>
-      <c r="C1" s="343"/>
-      <c r="D1" s="343"/>
-      <c r="E1" s="343"/>
-      <c r="F1" s="343"/>
-      <c r="G1" s="343"/>
-      <c r="H1" s="343"/>
-      <c r="I1" s="343"/>
-      <c r="J1" s="343"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="344" t="s">
+      <c r="B1" s="346"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="347" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="345"/>
-      <c r="C2" s="345"/>
-      <c r="D2" s="345"/>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
-      <c r="G2" s="345"/>
-      <c r="H2" s="345"/>
-      <c r="I2" s="345"/>
-      <c r="J2" s="345"/>
-    </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="348"/>
+      <c r="C2" s="348"/>
+      <c r="D2" s="348"/>
+      <c r="E2" s="348"/>
+      <c r="F2" s="348"/>
+      <c r="G2" s="348"/>
+      <c r="H2" s="348"/>
+      <c r="I2" s="348"/>
+      <c r="J2" s="348"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" thickBot="1">
       <c r="A4" s="350" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="343"/>
-      <c r="C4" s="343"/>
-      <c r="D4" s="343"/>
-      <c r="E4" s="343"/>
-      <c r="F4" s="343"/>
-      <c r="G4" s="343"/>
-      <c r="H4" s="343"/>
-      <c r="I4" s="343"/>
-      <c r="J4" s="343"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="346"/>
+      <c r="C4" s="346"/>
+      <c r="D4" s="346"/>
+      <c r="E4" s="346"/>
+      <c r="F4" s="346"/>
+      <c r="G4" s="346"/>
+      <c r="H4" s="346"/>
+      <c r="I4" s="346"/>
+      <c r="J4" s="346"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B5" s="32">
         <v>135</v>
       </c>
-      <c r="C5" s="354" t="s">
+      <c r="C5" s="351" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="351"/>
-      <c r="E5" s="351"/>
-      <c r="F5" s="351"/>
-      <c r="G5" s="351"/>
-      <c r="H5" s="351"/>
-      <c r="I5" s="351"/>
-      <c r="J5" s="351"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D5" s="352"/>
+      <c r="E5" s="352"/>
+      <c r="F5" s="352"/>
+      <c r="G5" s="352"/>
+      <c r="H5" s="352"/>
+      <c r="I5" s="352"/>
+      <c r="J5" s="352"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="350" t="s">
         <v>197</v>
       </c>
-      <c r="B7" s="343"/>
-      <c r="C7" s="343"/>
-      <c r="D7" s="343"/>
-      <c r="E7" s="343"/>
-      <c r="F7" s="343"/>
-      <c r="G7" s="343"/>
-      <c r="H7" s="343"/>
-      <c r="I7" s="343"/>
-      <c r="J7" s="343"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="346"/>
+      <c r="C7" s="346"/>
+      <c r="D7" s="346"/>
+      <c r="E7" s="346"/>
+      <c r="F7" s="346"/>
+      <c r="G7" s="346"/>
+      <c r="H7" s="346"/>
+      <c r="I7" s="346"/>
+      <c r="J7" s="346"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="6"/>
       <c r="B8" s="52" t="s">
         <v>118</v>
@@ -37572,7 +37588,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
         <v>198</v>
       </c>
@@ -37592,7 +37608,7 @@
       <c r="F9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>426</v>
       </c>
@@ -37609,7 +37625,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>199</v>
       </c>
@@ -37630,7 +37646,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>201</v>
       </c>
@@ -37651,7 +37667,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>203</v>
       </c>
@@ -37672,7 +37688,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
         <v>205</v>
       </c>
@@ -37694,12 +37710,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10">
       <c r="B15" s="54"/>
       <c r="C15" s="54"/>
       <c r="D15" s="54"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16" s="6" t="s">
         <v>207</v>
       </c>
@@ -37721,7 +37737,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
         <v>239</v>
       </c>
@@ -37746,7 +37762,7 @@
       <c r="I17" s="145"/>
       <c r="J17" s="145"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
         <v>241</v>
       </c>
@@ -37771,21 +37787,21 @@
       <c r="I18" s="145"/>
       <c r="J18" s="145"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20" s="350" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="343"/>
-      <c r="C20" s="343"/>
-      <c r="D20" s="343"/>
-      <c r="E20" s="343"/>
-      <c r="F20" s="343"/>
-      <c r="G20" s="343"/>
-      <c r="H20" s="343"/>
-      <c r="I20" s="343"/>
-      <c r="J20" s="343"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="346"/>
+      <c r="C20" s="346"/>
+      <c r="D20" s="346"/>
+      <c r="E20" s="346"/>
+      <c r="F20" s="346"/>
+      <c r="G20" s="346"/>
+      <c r="H20" s="346"/>
+      <c r="I20" s="346"/>
+      <c r="J20" s="346"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="6"/>
       <c r="B21" s="52" t="s">
         <v>118</v>
@@ -37803,7 +37819,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>244</v>
       </c>
@@ -37820,7 +37836,7 @@
         <v>44.457344759072257</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>209</v>
       </c>
@@ -37837,7 +37853,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10">
       <c r="A24" s="7" t="s">
         <v>210</v>
       </c>
@@ -37860,21 +37876,21 @@
       <c r="I24" s="150"/>
       <c r="J24" s="150"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10">
       <c r="A26" s="350" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="343"/>
-      <c r="C26" s="343"/>
-      <c r="D26" s="343"/>
-      <c r="E26" s="343"/>
-      <c r="F26" s="343"/>
-      <c r="G26" s="343"/>
-      <c r="H26" s="343"/>
-      <c r="I26" s="343"/>
-      <c r="J26" s="343"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="346"/>
+      <c r="C26" s="346"/>
+      <c r="D26" s="346"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
+      <c r="G26" s="346"/>
+      <c r="H26" s="346"/>
+      <c r="I26" s="346"/>
+      <c r="J26" s="346"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="6" t="s">
         <v>19</v>
       </c>
@@ -37896,7 +37912,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -37916,7 +37932,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>152</v>
       </c>
@@ -37936,7 +37952,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -37956,43 +37972,43 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="352" t="s">
+    <row r="31" spans="1:10">
+      <c r="A31" s="353" t="s">
         <v>413</v>
       </c>
-      <c r="B31" s="351"/>
-      <c r="C31" s="351"/>
-      <c r="D31" s="351"/>
-      <c r="E31" s="351"/>
-      <c r="F31" s="351"/>
-      <c r="G31" s="351"/>
-      <c r="H31" s="351"/>
-      <c r="I31" s="351"/>
-      <c r="J31" s="351"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="352"/>
+      <c r="C31" s="352"/>
+      <c r="D31" s="352"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
+      <c r="G31" s="352"/>
+      <c r="H31" s="352"/>
+      <c r="I31" s="352"/>
+      <c r="J31" s="352"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="B33" s="343"/>
-      <c r="C33" s="343"/>
-      <c r="D33" s="343"/>
-      <c r="E33" s="343"/>
-      <c r="F33" s="343"/>
-      <c r="G33" s="343"/>
-      <c r="H33" s="343"/>
-      <c r="I33" s="343"/>
-      <c r="J33" s="343"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="346"/>
+      <c r="C33" s="346"/>
+      <c r="D33" s="346"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
+      <c r="G33" s="346"/>
+      <c r="H33" s="346"/>
+      <c r="I33" s="346"/>
+      <c r="J33" s="346"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B34" s="353" t="s">
+      <c r="B34" s="354" t="s">
         <v>164</v>
       </c>
-      <c r="C34" s="353"/>
-      <c r="D34" s="353"/>
+      <c r="C34" s="354"/>
+      <c r="D34" s="354"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -38002,7 +38018,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>215</v>
       </c>
@@ -38024,7 +38040,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>119</v>
       </c>
@@ -38041,7 +38057,7 @@
         <v>86.78608772314054</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10">
       <c r="A37" s="7" t="s">
         <v>217</v>
       </c>
@@ -38064,21 +38080,21 @@
       <c r="I37" s="150"/>
       <c r="J37" s="150"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10">
       <c r="A39" s="350" t="s">
         <v>425</v>
       </c>
-      <c r="B39" s="343"/>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-      <c r="G39" s="343"/>
-      <c r="H39" s="343"/>
-      <c r="I39" s="343"/>
-      <c r="J39" s="343"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B39" s="346"/>
+      <c r="C39" s="346"/>
+      <c r="D39" s="346"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
+      <c r="G39" s="346"/>
+      <c r="H39" s="346"/>
+      <c r="I39" s="346"/>
+      <c r="J39" s="346"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="6" t="s">
         <v>218</v>
       </c>
@@ -38107,7 +38123,7 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10">
       <c r="A41" s="28">
         <f>SOTP!B52</f>
         <v>5.5445352564102546E-2</v>
@@ -38133,7 +38149,7 @@
         <v>125.58383681411505</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10">
       <c r="A42" s="28">
         <f>SOTP!B53</f>
         <v>6.5445352564102555E-2</v>
@@ -38159,7 +38175,7 @@
         <v>77.338240421890944</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10">
       <c r="A43" s="28">
         <f>SOTP!B54</f>
         <v>7.544535256410255E-2</v>
@@ -38185,7 +38201,7 @@
         <v>56.458010524112666</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10">
       <c r="A44" s="28">
         <f>SOTP!B55</f>
         <v>8.5445352564102545E-2</v>
@@ -38211,7 +38227,7 @@
         <v>44.868194990164753</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10">
       <c r="A45" s="28">
         <f>SOTP!B56</f>
         <v>9.5445352564102554E-2</v>
@@ -38237,21 +38253,21 @@
         <v>37.534533839102714</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10">
       <c r="A48" s="350" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="343"/>
-      <c r="C48" s="343"/>
-      <c r="D48" s="343"/>
-      <c r="E48" s="343"/>
-      <c r="F48" s="343"/>
-      <c r="G48" s="343"/>
-      <c r="H48" s="343"/>
-      <c r="I48" s="343"/>
-      <c r="J48" s="343"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B48" s="346"/>
+      <c r="C48" s="346"/>
+      <c r="D48" s="346"/>
+      <c r="E48" s="346"/>
+      <c r="F48" s="346"/>
+      <c r="G48" s="346"/>
+      <c r="H48" s="346"/>
+      <c r="I48" s="346"/>
+      <c r="J48" s="346"/>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="6" t="s">
         <v>220</v>
       </c>
@@ -38273,7 +38289,7 @@
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10">
       <c r="A50" s="1" t="s">
         <v>222</v>
       </c>
@@ -38288,7 +38304,7 @@
         <v>4694</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>223</v>
       </c>
@@ -38305,7 +38321,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>224</v>
       </c>
@@ -38322,7 +38338,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>225</v>
       </c>
@@ -38339,7 +38355,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>226</v>
       </c>
@@ -38356,7 +38372,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>227</v>
       </c>
@@ -38373,7 +38389,7 @@
         <v>-662</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>228</v>
       </c>
@@ -38390,7 +38406,7 @@
         <v>-2469</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>229</v>
       </c>
@@ -38405,7 +38421,7 @@
       </c>
       <c r="E57" s="92"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10">
       <c r="A58" s="1" t="s">
         <v>230</v>
       </c>
@@ -38422,7 +38438,7 @@
         <v>-10107</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>231</v>
       </c>
@@ -38439,21 +38455,21 @@
         <v>-4276</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10">
       <c r="A62" s="350" t="s">
         <v>311</v>
       </c>
-      <c r="B62" s="351"/>
-      <c r="C62" s="351"/>
-      <c r="D62" s="351"/>
-      <c r="E62" s="351"/>
-      <c r="F62" s="351"/>
-      <c r="G62" s="351"/>
-      <c r="H62" s="351"/>
-      <c r="I62" s="351"/>
-      <c r="J62" s="351"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="352"/>
+      <c r="C62" s="352"/>
+      <c r="D62" s="352"/>
+      <c r="E62" s="352"/>
+      <c r="F62" s="352"/>
+      <c r="G62" s="352"/>
+      <c r="H62" s="352"/>
+      <c r="I62" s="352"/>
+      <c r="J62" s="352"/>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="6" t="s">
         <v>299</v>
       </c>
@@ -38475,7 +38491,7 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>302</v>
       </c>
@@ -38494,7 +38510,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>312</v>
       </c>
@@ -38510,7 +38526,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>313</v>
       </c>
@@ -38526,7 +38542,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>314</v>
       </c>
@@ -38542,7 +38558,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>315</v>
       </c>
@@ -38558,7 +38574,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>316</v>
       </c>
@@ -38575,7 +38591,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>310</v>
       </c>
@@ -38594,12 +38610,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A7:J7"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A31:J31"/>
@@ -38607,6 +38617,12 @@
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -38619,41 +38635,41 @@
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
   <dimension ref="A1:I66"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="7" width="22.21875" customWidth="1"/>
     <col min="8" max="14" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4" s="3"/>
       <c r="H4" s="336"/>
       <c r="I4" s="337"/>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15" thickBot="1">
       <c r="A5" s="170" t="s">
         <v>417</v>
       </c>
       <c r="H5" s="338"/>
       <c r="I5" s="337"/>
     </row>
-    <row r="6" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" thickTop="1">
       <c r="A6" s="179" t="s">
         <v>149</v>
       </c>
@@ -38666,7 +38682,7 @@
       <c r="H6" s="338"/>
       <c r="I6" s="337"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7" s="177" t="s">
         <v>19</v>
       </c>
@@ -38689,7 +38705,7 @@
       <c r="H7" s="339"/>
       <c r="I7" s="337"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8" s="178" t="s">
         <v>35</v>
       </c>
@@ -38715,7 +38731,7 @@
       </c>
       <c r="G8" s="200"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9" s="178" t="s">
         <v>152</v>
       </c>
@@ -38741,7 +38757,7 @@
       </c>
       <c r="G9" s="200"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10" s="178" t="s">
         <v>153</v>
       </c>
@@ -38767,7 +38783,7 @@
       </c>
       <c r="G10" s="200"/>
     </row>
-    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="15" thickBot="1">
       <c r="A11" s="182" t="s">
         <v>154</v>
       </c>
@@ -38790,14 +38806,14 @@
       <c r="F11" s="193"/>
       <c r="G11" s="202"/>
     </row>
-    <row r="12" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="15.6" thickTop="1" thickBot="1">
       <c r="B12" s="54"/>
       <c r="C12" s="54"/>
       <c r="D12" s="54"/>
       <c r="E12" s="54"/>
       <c r="F12" s="81"/>
     </row>
-    <row r="13" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" thickTop="1">
       <c r="A13" s="187"/>
       <c r="B13" s="180"/>
       <c r="C13" s="180"/>
@@ -38806,7 +38822,7 @@
       <c r="F13" s="260"/>
       <c r="G13" s="181"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14" s="185"/>
       <c r="B14" s="52" t="s">
         <v>118</v>
@@ -38823,7 +38839,7 @@
       </c>
       <c r="G14" s="206"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15" s="186" t="s">
         <v>154</v>
       </c>
@@ -38842,7 +38858,7 @@
       <c r="E15" s="54"/>
       <c r="G15" s="207"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16" s="186" t="s">
         <v>156</v>
       </c>
@@ -38863,7 +38879,7 @@
       </c>
       <c r="G16" s="208"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="186" t="s">
         <v>157</v>
       </c>
@@ -38884,7 +38900,7 @@
       </c>
       <c r="G17" s="208"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="186" t="s">
         <v>158</v>
       </c>
@@ -38905,7 +38921,7 @@
       </c>
       <c r="G18" s="208"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="186" t="s">
         <v>159</v>
       </c>
@@ -38923,7 +38939,7 @@
       <c r="E19" s="54"/>
       <c r="G19" s="207"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15" thickBot="1">
       <c r="A20" s="182" t="s">
         <v>160</v>
       </c>
@@ -38943,13 +38959,13 @@
       <c r="F20" s="261"/>
       <c r="G20" s="209"/>
     </row>
-    <row r="21" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="15.6" thickTop="1" thickBot="1">
       <c r="B21" s="54"/>
       <c r="C21" s="54"/>
       <c r="D21" s="54"/>
       <c r="E21" s="54"/>
     </row>
-    <row r="22" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="15" thickTop="1">
       <c r="A22" s="179" t="s">
         <v>161</v>
       </c>
@@ -38960,7 +38976,7 @@
       <c r="F22" s="262"/>
       <c r="G22" s="210"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="177" t="s">
         <v>6</v>
       </c>
@@ -38979,7 +38995,7 @@
       </c>
       <c r="G23" s="206"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="186" t="s">
         <v>235</v>
       </c>
@@ -39000,7 +39016,7 @@
       </c>
       <c r="G24" s="208"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="186" t="s">
         <v>236</v>
       </c>
@@ -39021,7 +39037,7 @@
       </c>
       <c r="G25" s="208"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="188" t="s">
         <v>237</v>
       </c>
@@ -39041,7 +39057,7 @@
       <c r="F26" s="263"/>
       <c r="G26" s="211"/>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15" thickBot="1">
       <c r="A27" s="189" t="s">
         <v>238</v>
       </c>
@@ -39061,14 +39077,14 @@
       <c r="F27" s="264"/>
       <c r="G27" s="212"/>
     </row>
-    <row r="28" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="15.6" thickTop="1" thickBot="1">
       <c r="B28" s="54"/>
       <c r="C28" s="54"/>
       <c r="D28" s="54"/>
       <c r="E28" s="54"/>
       <c r="F28" s="81"/>
     </row>
-    <row r="29" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="15" thickTop="1">
       <c r="A29" s="187" t="s">
         <v>162</v>
       </c>
@@ -39079,7 +39095,7 @@
       <c r="F29" s="265"/>
       <c r="G29" s="191"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" s="185" t="s">
         <v>19</v>
       </c>
@@ -39100,7 +39116,7 @@
       </c>
       <c r="G30" s="176"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" s="186" t="s">
         <v>35</v>
       </c>
@@ -39125,7 +39141,7 @@
       </c>
       <c r="G31" s="184"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" s="186" t="s">
         <v>152</v>
       </c>
@@ -39150,7 +39166,7 @@
       </c>
       <c r="G32" s="184"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" s="186" t="s">
         <v>170</v>
       </c>
@@ -39175,7 +39191,7 @@
       </c>
       <c r="G33" s="184"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15" thickBot="1">
       <c r="A34" s="182" t="s">
         <v>172</v>
       </c>
@@ -39194,14 +39210,14 @@
       <c r="F34" s="266"/>
       <c r="G34" s="195"/>
     </row>
-    <row r="35" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="15.6" thickTop="1" thickBot="1">
       <c r="B35" s="54"/>
       <c r="C35" s="54"/>
       <c r="D35" s="54"/>
       <c r="E35" s="54"/>
       <c r="F35" s="81"/>
     </row>
-    <row r="36" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="15" thickTop="1">
       <c r="A36" s="179" t="s">
         <v>173</v>
       </c>
@@ -39212,7 +39228,7 @@
       <c r="F36" s="265"/>
       <c r="G36" s="191"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" s="177" t="s">
         <v>174</v>
       </c>
@@ -39233,7 +39249,7 @@
       </c>
       <c r="G37" s="176"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" s="186" t="s">
         <v>1</v>
       </c>
@@ -39254,7 +39270,7 @@
       </c>
       <c r="G38" s="184"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" s="186" t="s">
         <v>177</v>
       </c>
@@ -39275,7 +39291,7 @@
       </c>
       <c r="G39" s="184"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" s="186" t="s">
         <v>179</v>
       </c>
@@ -39296,7 +39312,7 @@
       </c>
       <c r="G40" s="184"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" s="186" t="s">
         <v>181</v>
       </c>
@@ -39317,7 +39333,7 @@
       </c>
       <c r="G41" s="184"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" s="186" t="s">
         <v>183</v>
       </c>
@@ -39338,7 +39354,7 @@
       </c>
       <c r="G42" s="184"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" s="186" t="s">
         <v>185</v>
       </c>
@@ -39355,7 +39371,7 @@
       <c r="F43" s="267"/>
       <c r="G43" s="196"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" s="186" t="s">
         <v>186</v>
       </c>
@@ -39376,7 +39392,7 @@
       </c>
       <c r="G44" s="184"/>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="15" thickBot="1">
       <c r="A45" s="197" t="s">
         <v>188</v>
       </c>
@@ -39397,17 +39413,17 @@
       </c>
       <c r="G45" s="199"/>
     </row>
-    <row r="46" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="15" thickTop="1">
       <c r="A46" s="47" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" s="47" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" s="350" t="s">
         <v>423</v>
       </c>
@@ -39418,12 +39434,12 @@
       <c r="F48" s="350"/>
       <c r="G48" s="350"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="22" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="22"/>
       <c r="B51" s="138" t="s">
         <v>190</v>
@@ -39444,7 +39460,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="22" t="s">
         <v>191</v>
       </c>
@@ -39473,7 +39489,7 @@
         <v>125.58383681411505</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="B53" s="251">
         <f>'Conn DCF'!B45-0.01</f>
         <v>6.5445352564102555E-2</v>
@@ -39499,7 +39515,7 @@
         <v>77.338240421890944</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="B54" s="251">
         <f>'Conn DCF'!B45</f>
         <v>7.544535256410255E-2</v>
@@ -39525,7 +39541,7 @@
         <v>56.458010524112666</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="B55" s="251">
         <f>'Conn DCF'!B45+0.01</f>
         <v>8.5445352564102545E-2</v>
@@ -39551,7 +39567,7 @@
         <v>44.868194990164753</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="B56" s="251">
         <f>'Conn DCF'!B45+0.02</f>
         <v>9.5445352564102554E-2</v>
@@ -39577,28 +39593,28 @@
         <v>37.534533839102714</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="C57" s="54"/>
       <c r="D57" s="54"/>
       <c r="E57" s="54"/>
       <c r="F57" s="54"/>
       <c r="G57" s="54"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="C58" s="54"/>
       <c r="D58" s="54"/>
       <c r="E58" s="54"/>
       <c r="F58" s="54"/>
       <c r="G58" s="54"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="C59" s="54"/>
       <c r="D59" s="54"/>
       <c r="E59" s="54"/>
       <c r="F59" s="54"/>
       <c r="G59" s="54"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="22" t="s">
         <v>192</v>
       </c>
@@ -39608,7 +39624,7 @@
       <c r="F60" s="54"/>
       <c r="G60" s="54"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="B61" s="66" t="s">
         <v>190</v>
       </c>
@@ -39628,7 +39644,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
         <v>191</v>
       </c>
@@ -39657,7 +39673,7 @@
         <v>1626105.5251109309</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="B63" s="60">
         <f>'Conn DCF'!B45-0.01</f>
         <v>6.5445352564102555E-2</v>
@@ -39683,7 +39699,7 @@
         <v>1000842.5958677067</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="B64" s="60">
         <f>'Conn DCF'!B45</f>
         <v>7.544535256410255E-2</v>
@@ -39709,7 +39725,7 @@
         <v>730234.81639250019</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:7">
       <c r="B65" s="60">
         <f>'Conn DCF'!B45+0.01</f>
         <v>8.5445352564102545E-2</v>
@@ -39735,7 +39751,7 @@
         <v>580030.80707253516</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:7">
       <c r="B66" s="60">
         <f>'Conn DCF'!B45+0.02</f>
         <v>9.5445352564102554E-2</v>
@@ -39786,27 +39802,27 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:X135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
     <col min="4" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="3"/>
     </row>
-    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="18">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -39822,7 +39838,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="5" t="s">
         <v>63</v>
       </c>
@@ -39850,7 +39866,7 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" s="6"/>
       <c r="B8" s="52" t="s">
         <v>64</v>
@@ -39922,7 +39938,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -39990,7 +40006,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -40058,7 +40074,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -40126,7 +40142,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -40194,7 +40210,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>81</v>
       </c>
@@ -40262,7 +40278,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -40293,7 +40309,7 @@
       <c r="W14" s="54"/>
       <c r="X14" s="54"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -40324,7 +40340,7 @@
       <c r="W15" s="54"/>
       <c r="X15" s="54"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -40349,7 +40365,7 @@
       <c r="W16" s="54"/>
       <c r="X16" s="54"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="A17" s="5" t="s">
         <v>83</v>
       </c>
@@ -40377,7 +40393,7 @@
       <c r="W17" s="90"/>
       <c r="X17" s="90"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="A18" s="6"/>
       <c r="B18" s="52" t="s">
         <v>64</v>
@@ -40449,7 +40465,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -40517,7 +40533,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -40585,7 +40601,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -40653,7 +40669,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -40721,7 +40737,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>81</v>
       </c>
@@ -40789,7 +40805,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -40820,7 +40836,7 @@
       <c r="W24" s="54"/>
       <c r="X24" s="54"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -40851,7 +40867,7 @@
       <c r="W25" s="54"/>
       <c r="X25" s="54"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -40876,7 +40892,7 @@
       <c r="W26" s="54"/>
       <c r="X26" s="54"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="A27" s="5" t="s">
         <v>84</v>
       </c>
@@ -40904,7 +40920,7 @@
       <c r="W27" s="90"/>
       <c r="X27" s="90"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" s="6"/>
       <c r="B28" s="52" t="s">
         <v>64</v>
@@ -40976,7 +40992,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -41044,7 +41060,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>78</v>
       </c>
@@ -41112,7 +41128,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -41180,7 +41196,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -41248,7 +41264,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -41316,7 +41332,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -41347,7 +41363,7 @@
       <c r="W34" s="54"/>
       <c r="X34" s="54"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -41378,7 +41394,7 @@
       <c r="W35" s="54"/>
       <c r="X35" s="54"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
       <c r="D36" s="54"/>
@@ -41403,7 +41419,7 @@
       <c r="W36" s="54"/>
       <c r="X36" s="54"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="5" t="s">
         <v>85</v>
       </c>
@@ -41431,7 +41447,7 @@
       <c r="W37" s="90"/>
       <c r="X37" s="90"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="6"/>
       <c r="B38" s="52" t="s">
         <v>64</v>
@@ -41503,7 +41519,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -41591,7 +41607,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -41679,7 +41695,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -41767,7 +41783,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -41855,7 +41871,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -41943,7 +41959,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -41974,7 +41990,7 @@
       <c r="W44" s="54"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -42005,7 +42021,7 @@
       <c r="W45" s="54"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24">
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
@@ -42030,7 +42046,7 @@
       <c r="W46" s="54"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24">
       <c r="A47" s="5" t="s">
         <v>86</v>
       </c>
@@ -42058,7 +42074,7 @@
       <c r="W47" s="90"/>
       <c r="X47" s="90"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24">
       <c r="A48" s="6"/>
       <c r="B48" s="52" t="s">
         <v>64</v>
@@ -42130,7 +42146,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -42225,7 +42241,7 @@
         <v>102808.68508469728</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -42321,7 +42337,7 @@
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -42416,7 +42432,7 @@
         <v>71966.07955928809</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -42513,7 +42529,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -42607,7 +42623,7 @@
         <v>11822.998784740188</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -42704,7 +42720,7 @@
         <v>60143.080774547903</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -42801,7 +42817,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>95</v>
       </c>
@@ -42898,7 +42914,7 @@
         <v>12630.046962655058</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>96</v>
       </c>
@@ -42995,7 +43011,7 @@
         <v>47513.033811892848</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24">
       <c r="A58" t="s">
         <v>97</v>
       </c>
@@ -43092,7 +43108,7 @@
         <v>11822.998784740188</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -43186,7 +43202,7 @@
         <v>-8224.6948067757821</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -43280,7 +43296,7 @@
         <v>-44.91641581370277</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24">
       <c r="A61" s="19" t="s">
         <v>100</v>
       </c>
@@ -43377,7 +43393,7 @@
         <v>51066.421374043552</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24">
       <c r="A62" t="s">
         <v>101</v>
       </c>
@@ -43474,7 +43490,7 @@
         <v>0.49671310679611652</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24">
       <c r="B63" s="92"/>
       <c r="C63" s="92"/>
       <c r="D63" s="92"/>
@@ -43499,7 +43515,7 @@
       <c r="W63" s="92"/>
       <c r="X63" s="92"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24">
       <c r="A64" s="5" t="s">
         <v>102</v>
       </c>
@@ -43527,7 +43543,7 @@
       <c r="W64" s="128"/>
       <c r="X64" s="128"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24">
       <c r="A65" s="6"/>
       <c r="B65" s="52"/>
       <c r="C65" s="52"/>
@@ -43593,7 +43609,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24">
       <c r="A66" t="s">
         <v>103</v>
       </c>
@@ -43661,7 +43677,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24">
       <c r="A67" t="s">
         <v>104</v>
       </c>
@@ -43749,7 +43765,7 @@
         <v>0.24211808525137521</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24">
       <c r="A68" t="s">
         <v>105</v>
       </c>
@@ -43837,7 +43853,7 @@
         <v>51066.421374043552</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24">
       <c r="A69" t="s">
         <v>106</v>
       </c>
@@ -43925,7 +43941,7 @@
         <v>12364.104163723327</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24">
       <c r="B70" s="54"/>
       <c r="C70" s="54"/>
       <c r="D70" s="54"/>
@@ -43950,7 +43966,7 @@
       <c r="W70" s="54"/>
       <c r="X70" s="54"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24">
       <c r="A71" s="5" t="s">
         <v>107</v>
       </c>
@@ -43978,7 +43994,7 @@
       <c r="W71" s="90"/>
       <c r="X71" s="90"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24">
       <c r="A72" s="1" t="s">
         <v>108</v>
       </c>
@@ -44006,7 +44022,7 @@
       <c r="W72" s="54"/>
       <c r="X72" s="54"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24">
       <c r="A73" t="s">
         <v>109</v>
       </c>
@@ -44037,7 +44053,7 @@
       <c r="W73" s="54"/>
       <c r="X73" s="54"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -44068,7 +44084,7 @@
       <c r="W74" s="54"/>
       <c r="X74" s="54"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -44099,7 +44115,7 @@
       <c r="W75" s="54"/>
       <c r="X75" s="54"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -44130,7 +44146,7 @@
       <c r="W76" s="54"/>
       <c r="X76" s="54"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24">
       <c r="B77" s="54"/>
       <c r="C77" s="54"/>
       <c r="D77" s="54"/>
@@ -44155,7 +44171,7 @@
       <c r="W77" s="54"/>
       <c r="X77" s="54"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24">
       <c r="A78" s="1" t="s">
         <v>113</v>
       </c>
@@ -44183,7 +44199,7 @@
       <c r="W78" s="54"/>
       <c r="X78" s="54"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24">
       <c r="A79" t="s">
         <v>687</v>
       </c>
@@ -44217,7 +44233,7 @@
       <c r="W79" s="54"/>
       <c r="X79" s="54"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24">
       <c r="A80" t="s">
         <v>114</v>
       </c>
@@ -44248,7 +44264,7 @@
       <c r="W80" s="54"/>
       <c r="X80" s="54"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -44279,7 +44295,7 @@
       <c r="W81" s="54"/>
       <c r="X81" s="54"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24">
       <c r="A82" t="s">
         <v>116</v>
       </c>
@@ -44310,7 +44326,7 @@
       <c r="W82" s="54"/>
       <c r="X82" s="54"/>
     </row>
-    <row r="83" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:24" ht="15" thickBot="1">
       <c r="B83" s="54"/>
       <c r="C83" s="54"/>
       <c r="D83" s="54"/>
@@ -44335,7 +44351,7 @@
       <c r="W83" s="54"/>
       <c r="X83" s="54"/>
     </row>
-    <row r="84" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" ht="15" thickTop="1">
       <c r="A84" s="9" t="s">
         <v>117</v>
       </c>
@@ -44363,7 +44379,7 @@
       <c r="W84" s="133"/>
       <c r="X84" s="133"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24">
       <c r="A85" s="10"/>
       <c r="B85" s="112" t="s">
         <v>118</v>
@@ -44393,7 +44409,7 @@
       <c r="W85" s="135"/>
       <c r="X85" s="135"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24">
       <c r="A86" s="11" t="s">
         <v>120</v>
       </c>
@@ -44427,7 +44443,7 @@
       <c r="W86" s="54"/>
       <c r="X86" s="54"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24">
       <c r="A87" s="11" t="s">
         <v>121</v>
       </c>
@@ -44461,7 +44477,7 @@
       <c r="W87" s="54"/>
       <c r="X87" s="54"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24">
       <c r="A88" s="20" t="s">
         <v>122</v>
       </c>
@@ -44495,7 +44511,7 @@
       <c r="W88" s="54"/>
       <c r="X88" s="54"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24">
       <c r="A89" s="11"/>
       <c r="B89" s="92"/>
       <c r="C89" s="106"/>
@@ -44521,7 +44537,7 @@
       <c r="W89" s="54"/>
       <c r="X89" s="54"/>
     </row>
-    <row r="90" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:24" ht="15" thickBot="1">
       <c r="A90" s="12" t="s">
         <v>123</v>
       </c>
@@ -44555,7 +44571,7 @@
       <c r="W90" s="54"/>
       <c r="X90" s="54"/>
     </row>
-    <row r="91" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" ht="15" thickTop="1">
       <c r="B91" s="54"/>
       <c r="C91" s="54"/>
       <c r="D91" s="54"/>
@@ -44580,7 +44596,7 @@
       <c r="W91" s="54"/>
       <c r="X91" s="54"/>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24">
       <c r="A92" s="5" t="s">
         <v>124</v>
       </c>
@@ -44608,12 +44624,12 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24">
       <c r="A94" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24">
       <c r="B96" s="138" t="s">
         <v>126</v>
       </c>
@@ -44638,7 +44654,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="B97" s="43">
         <f>$B$45-0.02</f>
         <v>5.5445352564102546E-2</v>
@@ -44664,7 +44680,7 @@
         <v>1502955.4753810572</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="B98" s="43">
         <f>$B$45-0.01</f>
         <v>6.5445352564102555E-2</v>
@@ -44690,7 +44706,7 @@
         <v>877692.54613783304</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="B99" s="43">
         <f>$B$45</f>
         <v>7.544535256410255E-2</v>
@@ -44716,7 +44732,7 @@
         <v>607084.76666262664</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="B100" s="43">
         <f>$B$45+0.01</f>
         <v>8.5445352564102545E-2</v>
@@ -44742,7 +44758,7 @@
         <v>456880.7573426615</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="B101" s="43">
         <f>$B$45+0.02</f>
         <v>9.5445352564102554E-2</v>
@@ -44768,12 +44784,12 @@
         <v>361836.50882489758</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="21" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="B106" s="66" t="s">
         <v>256</v>
       </c>
@@ -44798,7 +44814,7 @@
         <v>15.925319738464918</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="B107" s="27">
         <f>$X$40-0.06</f>
         <v>0.6399999999999999</v>
@@ -44824,7 +44840,7 @@
         <v>498013.06242870615</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="B108" s="27">
         <f>$X$40-0.03</f>
         <v>0.66999999999999993</v>
@@ -44850,7 +44866,7 @@
         <v>509905.3787009925</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="B109" s="27">
         <f>$X$40</f>
         <v>0.7</v>
@@ -44876,7 +44892,7 @@
         <v>521797.69497327891</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="B110" s="27">
         <f>$X$40+0.03</f>
         <v>0.73</v>
@@ -44902,7 +44918,7 @@
         <v>533690.01124556537</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="B111" s="27">
         <f>$X$40+0.06</f>
         <v>0.76</v>
@@ -44928,12 +44944,12 @@
         <v>545582.32751785172</v>
       </c>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24">
       <c r="A114" s="21" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24">
       <c r="B116" s="66" t="s">
         <v>127</v>
       </c>
@@ -44958,7 +44974,7 @@
         <v>15.925319738464918</v>
       </c>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24">
       <c r="B117" s="43">
         <f>$B$45-0.02</f>
         <v>5.5445352564102546E-2</v>
@@ -44984,7 +45000,7 @@
         <v>702569.71375334647</v>
       </c>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24">
       <c r="B118" s="43">
         <f>$B$45-0.01</f>
         <v>6.5445352564102555E-2</v>
@@ -45010,7 +45026,7 @@
         <v>604305.88030614099</v>
       </c>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24">
       <c r="B119" s="43">
         <f>$B$45</f>
         <v>7.544535256410255E-2</v>
@@ -45036,7 +45052,7 @@
         <v>521797.69497327891</v>
       </c>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24">
       <c r="B120" s="43">
         <f>$B$45+0.01</f>
         <v>8.5445352564102545E-2</v>
@@ -45062,7 +45078,7 @@
         <v>452321.92407721211</v>
       </c>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24">
       <c r="B121" s="43">
         <f>$B$45+0.02</f>
         <v>9.5445352564102554E-2</v>
@@ -45088,7 +45104,7 @@
         <v>393652.48720974184</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24">
       <c r="A124" s="350" t="s">
         <v>265</v>
       </c>
@@ -45116,7 +45132,7 @@
       <c r="W124" s="350"/>
       <c r="X124" s="350"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
         <v>266</v>
       </c>
@@ -45186,7 +45202,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -45254,7 +45270,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24">
       <c r="A127" t="s">
         <v>268</v>
       </c>
@@ -45322,7 +45338,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24">
       <c r="A128" t="s">
         <v>269</v>
       </c>
@@ -45411,7 +45427,7 @@
         <v>169.5</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24">
       <c r="A129" t="s">
         <v>270</v>
       </c>
@@ -45479,7 +45495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24">
       <c r="A130" t="s">
         <v>271</v>
       </c>
@@ -45568,7 +45584,7 @@
         <v>50850</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24">
       <c r="A131" t="s">
         <v>272</v>
       </c>
@@ -45656,7 +45672,7 @@
         <v>39460.024793902863</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24">
       <c r="A132" t="s">
         <v>273</v>
       </c>
@@ -45722,7 +45738,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24">
       <c r="A133" s="1" t="s">
         <v>274</v>
       </c>
@@ -45813,7 +45829,7 @@
         <v>90310.024793902863</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24">
       <c r="A134" t="s">
         <v>275</v>
       </c>
@@ -45902,7 +45918,7 @@
         <v>102808.68508469728</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24">
       <c r="A135" s="2" t="s">
         <v>276</v>
       </c>
@@ -46006,27 +46022,27 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:X134"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
     <col min="4" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="3"/>
     </row>
-    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="18">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -46042,7 +46058,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="5" t="s">
         <v>63</v>
       </c>
@@ -46070,7 +46086,7 @@
       <c r="W7" s="90"/>
       <c r="X7" s="90"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" s="6"/>
       <c r="B8" s="52" t="s">
         <v>64</v>
@@ -46142,7 +46158,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -46210,7 +46226,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -46278,7 +46294,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -46346,7 +46362,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -46414,7 +46430,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>81</v>
       </c>
@@ -46482,7 +46498,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -46513,7 +46529,7 @@
       <c r="W14" s="54"/>
       <c r="X14" s="54"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -46544,7 +46560,7 @@
       <c r="W15" s="54"/>
       <c r="X15" s="54"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -46569,7 +46585,7 @@
       <c r="W16" s="54"/>
       <c r="X16" s="54"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="A17" s="5" t="s">
         <v>83</v>
       </c>
@@ -46597,7 +46613,7 @@
       <c r="W17" s="90"/>
       <c r="X17" s="90"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="A18" s="6"/>
       <c r="B18" s="52" t="s">
         <v>64</v>
@@ -46669,7 +46685,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -46737,7 +46753,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -46805,7 +46821,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -46873,7 +46889,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -46941,7 +46957,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>81</v>
       </c>
@@ -47009,7 +47025,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -47040,7 +47056,7 @@
       <c r="W24" s="54"/>
       <c r="X24" s="54"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -47071,7 +47087,7 @@
       <c r="W25" s="54"/>
       <c r="X25" s="54"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -47096,7 +47112,7 @@
       <c r="W26" s="54"/>
       <c r="X26" s="54"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="A27" s="5" t="s">
         <v>84</v>
       </c>
@@ -47124,7 +47140,7 @@
       <c r="W27" s="90"/>
       <c r="X27" s="90"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" s="6"/>
       <c r="B28" s="52" t="s">
         <v>64</v>
@@ -47196,7 +47212,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -47264,7 +47280,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>78</v>
       </c>
@@ -47332,7 +47348,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -47400,7 +47416,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -47468,7 +47484,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -47536,7 +47552,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -47567,7 +47583,7 @@
       <c r="W34" s="54"/>
       <c r="X34" s="54"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -47598,7 +47614,7 @@
       <c r="W35" s="54"/>
       <c r="X35" s="54"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
       <c r="D36" s="54"/>
@@ -47623,7 +47639,7 @@
       <c r="W36" s="54"/>
       <c r="X36" s="54"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="5" t="s">
         <v>128</v>
       </c>
@@ -47651,7 +47667,7 @@
       <c r="W37" s="90"/>
       <c r="X37" s="90"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="6"/>
       <c r="B38" s="52" t="s">
         <v>64</v>
@@ -47723,7 +47739,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -47811,7 +47827,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -47899,7 +47915,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -47987,7 +48003,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -48075,7 +48091,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -48163,7 +48179,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -48194,7 +48210,7 @@
       <c r="W44" s="54"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -48225,7 +48241,7 @@
       <c r="W45" s="54"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24">
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
@@ -48250,7 +48266,7 @@
       <c r="W46" s="54"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24">
       <c r="A47" s="5" t="s">
         <v>129</v>
       </c>
@@ -48278,7 +48294,7 @@
       <c r="W47" s="90"/>
       <c r="X47" s="90"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24">
       <c r="A48" s="6"/>
       <c r="B48" s="52" t="s">
         <v>64</v>
@@ -48350,7 +48366,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -48445,7 +48461,7 @@
         <v>34482.477963923913</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -48539,7 +48555,7 @@
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -48634,7 +48650,7 @@
         <v>19310.187659797393</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -48731,7 +48747,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -48825,7 +48841,7 @@
         <v>3620.6601862120106</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -48922,7 +48938,7 @@
         <v>15689.527473585382</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -49019,7 +49035,7 @@
         <v>0.45500000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>130</v>
       </c>
@@ -49116,7 +49132,7 @@
         <v>3294.8007694529301</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>96</v>
       </c>
@@ -49213,7 +49229,7 @@
         <v>12394.726704132452</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24">
       <c r="A58" t="s">
         <v>97</v>
       </c>
@@ -49310,7 +49326,7 @@
         <v>3620.6601862120106</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -49404,7 +49420,7 @@
         <v>-3103.4230167531523</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -49498,7 +49514,7 @@
         <v>-15.065160275500784</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24">
       <c r="A61" s="19" t="s">
         <v>100</v>
       </c>
@@ -49595,7 +49611,7 @@
         <v>12896.89871331581</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24">
       <c r="A62" t="s">
         <v>101</v>
       </c>
@@ -49692,7 +49708,7 @@
         <v>0.37401310679611655</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24">
       <c r="B63" s="54"/>
       <c r="C63" s="54"/>
       <c r="D63" s="54"/>
@@ -49717,7 +49733,7 @@
       <c r="W63" s="54"/>
       <c r="X63" s="54"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24">
       <c r="A64" s="5" t="s">
         <v>102</v>
       </c>
@@ -49745,7 +49761,7 @@
       <c r="W64" s="97"/>
       <c r="X64" s="97"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24">
       <c r="A65" s="6"/>
       <c r="B65" s="52"/>
       <c r="C65" s="52"/>
@@ -49811,7 +49827,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24">
       <c r="A66" t="s">
         <v>103</v>
       </c>
@@ -49879,7 +49895,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24">
       <c r="A67" t="s">
         <v>104</v>
       </c>
@@ -49967,7 +49983,7 @@
         <v>0.22568428587799955</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24">
       <c r="A68" t="s">
         <v>105</v>
       </c>
@@ -50055,7 +50071,7 @@
         <v>12896.89871331581</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24">
       <c r="A69" t="s">
         <v>106</v>
       </c>
@@ -50143,7 +50159,7 @@
         <v>2910.6273761555699</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24">
       <c r="B70" s="54"/>
       <c r="C70" s="54"/>
       <c r="D70" s="54"/>
@@ -50168,7 +50184,7 @@
       <c r="W70" s="54"/>
       <c r="X70" s="54"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24">
       <c r="A71" s="5" t="s">
         <v>107</v>
       </c>
@@ -50196,7 +50212,7 @@
       <c r="W71" s="90"/>
       <c r="X71" s="90"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24">
       <c r="A72" s="1" t="s">
         <v>108</v>
       </c>
@@ -50224,7 +50240,7 @@
       <c r="W72" s="54"/>
       <c r="X72" s="54"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24">
       <c r="A73" t="s">
         <v>131</v>
       </c>
@@ -50255,7 +50271,7 @@
       <c r="W73" s="54"/>
       <c r="X73" s="54"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -50286,7 +50302,7 @@
       <c r="W74" s="54"/>
       <c r="X74" s="54"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -50317,7 +50333,7 @@
       <c r="W75" s="54"/>
       <c r="X75" s="54"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -50348,7 +50364,7 @@
       <c r="W76" s="54"/>
       <c r="X76" s="54"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24">
       <c r="B77" s="64"/>
       <c r="C77" s="64"/>
       <c r="D77" s="64"/>
@@ -50373,7 +50389,7 @@
       <c r="W77" s="54"/>
       <c r="X77" s="54"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24">
       <c r="A78" s="1" t="s">
         <v>113</v>
       </c>
@@ -50401,7 +50417,7 @@
       <c r="W78" s="54"/>
       <c r="X78" s="54"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24">
       <c r="A79" t="s">
         <v>687</v>
       </c>
@@ -50435,7 +50451,7 @@
       <c r="W79" s="54"/>
       <c r="X79" s="54"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24">
       <c r="A80" t="s">
         <v>114</v>
       </c>
@@ -50466,7 +50482,7 @@
       <c r="W80" s="54"/>
       <c r="X80" s="54"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -50497,7 +50513,7 @@
       <c r="W81" s="54"/>
       <c r="X81" s="54"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24">
       <c r="A82" t="s">
         <v>116</v>
       </c>
@@ -50528,7 +50544,7 @@
       <c r="W82" s="54"/>
       <c r="X82" s="54"/>
     </row>
-    <row r="83" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:24" ht="15" thickBot="1">
       <c r="B83" s="92"/>
       <c r="C83" s="92"/>
       <c r="D83" s="92"/>
@@ -50553,7 +50569,7 @@
       <c r="W83" s="54"/>
       <c r="X83" s="54"/>
     </row>
-    <row r="84" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" ht="15" thickTop="1">
       <c r="A84" s="9" t="s">
         <v>132</v>
       </c>
@@ -50581,7 +50597,7 @@
       <c r="W84" s="133"/>
       <c r="X84" s="133"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24">
       <c r="A85" s="10"/>
       <c r="B85" s="112" t="s">
         <v>118</v>
@@ -50611,7 +50627,7 @@
       <c r="W85" s="135"/>
       <c r="X85" s="135"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24">
       <c r="A86" s="11" t="s">
         <v>120</v>
       </c>
@@ -50645,7 +50661,7 @@
       <c r="W86" s="54"/>
       <c r="X86" s="54"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24">
       <c r="A87" s="11" t="s">
         <v>121</v>
       </c>
@@ -50679,7 +50695,7 @@
       <c r="W87" s="54"/>
       <c r="X87" s="54"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24">
       <c r="A88" s="20" t="s">
         <v>122</v>
       </c>
@@ -50713,7 +50729,7 @@
       <c r="W88" s="54"/>
       <c r="X88" s="54"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24">
       <c r="A89" s="11"/>
       <c r="B89" s="54"/>
       <c r="C89" s="71"/>
@@ -50739,7 +50755,7 @@
       <c r="W89" s="54"/>
       <c r="X89" s="54"/>
     </row>
-    <row r="90" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:24" ht="15" thickBot="1">
       <c r="A90" s="12" t="s">
         <v>123</v>
       </c>
@@ -50773,7 +50789,7 @@
       <c r="W90" s="54"/>
       <c r="X90" s="54"/>
     </row>
-    <row r="91" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" ht="15" thickTop="1">
       <c r="B91" s="54"/>
       <c r="C91" s="54"/>
       <c r="D91" s="54"/>
@@ -50798,7 +50814,7 @@
       <c r="W91" s="54"/>
       <c r="X91" s="54"/>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24">
       <c r="A92" s="5" t="s">
         <v>133</v>
       </c>
@@ -50826,12 +50842,12 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24">
       <c r="A94" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24">
       <c r="B96" s="66" t="s">
         <v>134</v>
       </c>
@@ -50856,7 +50872,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="B97" s="114">
         <f>$B$45-0.02</f>
         <v>5.9328831862053621E-2</v>
@@ -50882,7 +50898,7 @@
         <v>220270.36059251346</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="B98" s="114">
         <f>$B$45-0.01</f>
         <v>6.932883186205363E-2</v>
@@ -50908,7 +50924,7 @@
         <v>141252.45052303403</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="B99" s="114">
         <f>$B$45</f>
         <v>7.9328831862053625E-2</v>
@@ -50934,7 +50950,7 @@
         <v>98897.448256559845</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="B100" s="114">
         <f>$B$45+0.01</f>
         <v>8.932883186205362E-2</v>
@@ -50960,7 +50976,7 @@
         <v>72867.418251000447</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="B101" s="114">
         <f>$B$45+0.02</f>
         <v>9.9328831862053629E-2</v>
@@ -50986,7 +51002,7 @@
         <v>55480.945369867768</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="B102" s="54"/>
       <c r="C102" s="54"/>
       <c r="D102" s="54"/>
@@ -50994,7 +51010,7 @@
       <c r="F102" s="54"/>
       <c r="G102" s="54"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="B103" s="54"/>
       <c r="C103" s="54"/>
       <c r="D103" s="54"/>
@@ -51002,7 +51018,7 @@
       <c r="F103" s="54"/>
       <c r="G103" s="54"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="21" t="s">
         <v>135</v>
       </c>
@@ -51013,7 +51029,7 @@
       <c r="F104" s="54"/>
       <c r="G104" s="54"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="B105" s="54"/>
       <c r="C105" s="54"/>
       <c r="D105" s="54"/>
@@ -51021,7 +51037,7 @@
       <c r="F105" s="54"/>
       <c r="G105" s="54"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="B106" s="66" t="s">
         <v>136</v>
       </c>
@@ -51046,7 +51062,7 @@
         <v>23.138888888888889</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="B107" s="114">
         <f>$B$45-0.02</f>
         <v>5.9328831862053621E-2</v>
@@ -51072,7 +51088,7 @@
         <v>187169.47589457757</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="B108" s="114">
         <f>$B$45-0.01</f>
         <v>6.932883186205363E-2</v>
@@ -51098,7 +51114,7 @@
         <v>156941.96415052703</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="B109" s="114">
         <f>$B$45</f>
         <v>7.9328831862053625E-2</v>
@@ -51124,7 +51140,7 @@
         <v>131778.84978207198</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="B110" s="114">
         <f>$B$45+0.01</f>
         <v>8.932883186205362E-2</v>
@@ -51150,7 +51166,7 @@
         <v>110786.59037833812</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="B111" s="114">
         <f>$B$45+0.02</f>
         <v>9.9328831862053629E-2</v>
@@ -51176,7 +51192,7 @@
         <v>93236.606165480975</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24">
       <c r="A124" s="350" t="s">
         <v>285</v>
       </c>
@@ -51204,7 +51220,7 @@
       <c r="W124" s="350"/>
       <c r="X124" s="350"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
         <v>266</v>
       </c>
@@ -51274,7 +51290,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24">
       <c r="A126" t="s">
         <v>286</v>
       </c>
@@ -51342,7 +51358,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24">
       <c r="A127" t="s">
         <v>287</v>
       </c>
@@ -51431,7 +51447,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24">
       <c r="A128" t="s">
         <v>288</v>
       </c>
@@ -51499,7 +51515,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24">
       <c r="A129" t="s">
         <v>289</v>
       </c>
@@ -51588,7 +51604,7 @@
         <v>32850</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24">
       <c r="A130" t="s">
         <v>290</v>
       </c>
@@ -51676,7 +51692,7 @@
         <v>3492.779092187036</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24">
       <c r="A131" t="s">
         <v>273</v>
       </c>
@@ -51742,7 +51758,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24">
       <c r="A132" s="1" t="s">
         <v>274</v>
       </c>
@@ -51833,7 +51849,7 @@
         <v>36342.779092187033</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24">
       <c r="A133" t="s">
         <v>275</v>
       </c>
@@ -51922,7 +51938,7 @@
         <v>34482.477963923913</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24">
       <c r="A134" s="2" t="s">
         <v>276</v>
       </c>
@@ -52026,7 +52042,7 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:X135"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -52034,22 +52050,22 @@
     <col min="4" max="24" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24">
       <c r="A2" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="A3" s="24" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="18">
       <c r="A5" s="1" t="s">
         <v>61</v>
       </c>
@@ -52065,7 +52081,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="5" t="s">
         <v>63</v>
       </c>
@@ -52093,7 +52109,7 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" s="6"/>
       <c r="B8" s="52" t="s">
         <v>64</v>
@@ -52165,7 +52181,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>77</v>
       </c>
@@ -52233,7 +52249,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -52301,7 +52317,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>79</v>
       </c>
@@ -52369,7 +52385,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -52437,7 +52453,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>81</v>
       </c>
@@ -52505,7 +52521,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -52536,7 +52552,7 @@
       <c r="W14" s="54"/>
       <c r="X14" s="54"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -52567,7 +52583,7 @@
       <c r="W15" s="54"/>
       <c r="X15" s="54"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="B16" s="54"/>
       <c r="C16" s="54"/>
       <c r="D16" s="54"/>
@@ -52592,7 +52608,7 @@
       <c r="W16" s="54"/>
       <c r="X16" s="54"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24">
       <c r="A17" s="5" t="s">
         <v>83</v>
       </c>
@@ -52620,7 +52636,7 @@
       <c r="W17" s="90"/>
       <c r="X17" s="90"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24">
       <c r="A18" s="6"/>
       <c r="B18" s="52" t="s">
         <v>64</v>
@@ -52692,7 +52708,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>77</v>
       </c>
@@ -52760,7 +52776,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>78</v>
       </c>
@@ -52828,7 +52844,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>79</v>
       </c>
@@ -52896,7 +52912,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>80</v>
       </c>
@@ -52964,7 +52980,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>81</v>
       </c>
@@ -53032,7 +53048,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -53063,7 +53079,7 @@
       <c r="W24" s="54"/>
       <c r="X24" s="54"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -53094,7 +53110,7 @@
       <c r="W25" s="54"/>
       <c r="X25" s="54"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24">
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
@@ -53119,7 +53135,7 @@
       <c r="W26" s="54"/>
       <c r="X26" s="54"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24">
       <c r="A27" s="5" t="s">
         <v>84</v>
       </c>
@@ -53147,7 +53163,7 @@
       <c r="W27" s="90"/>
       <c r="X27" s="90"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24">
       <c r="A28" s="6"/>
       <c r="B28" s="52" t="s">
         <v>64</v>
@@ -53219,7 +53235,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>77</v>
       </c>
@@ -53287,7 +53303,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24">
       <c r="A30" t="s">
         <v>78</v>
       </c>
@@ -53355,7 +53371,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -53423,7 +53439,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>80</v>
       </c>
@@ -53491,7 +53507,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -53559,7 +53575,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -53590,7 +53606,7 @@
       <c r="W34" s="54"/>
       <c r="X34" s="54"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -53621,7 +53637,7 @@
       <c r="W35" s="54"/>
       <c r="X35" s="54"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24">
       <c r="B36" s="54"/>
       <c r="C36" s="54"/>
       <c r="D36" s="54"/>
@@ -53646,7 +53662,7 @@
       <c r="W36" s="54"/>
       <c r="X36" s="54"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24">
       <c r="A37" s="5" t="s">
         <v>128</v>
       </c>
@@ -53674,7 +53690,7 @@
       <c r="W37" s="90"/>
       <c r="X37" s="90"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24">
       <c r="A38" s="6"/>
       <c r="B38" s="52" t="s">
         <v>64</v>
@@ -53746,7 +53762,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -53834,7 +53850,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -53922,7 +53938,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -54010,7 +54026,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -54098,7 +54114,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -54186,7 +54202,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -54217,7 +54233,7 @@
       <c r="W44" s="54"/>
       <c r="X44" s="54"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -54248,7 +54264,7 @@
       <c r="W45" s="54"/>
       <c r="X45" s="54"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24">
       <c r="B46" s="54"/>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
@@ -54273,7 +54289,7 @@
       <c r="W46" s="54"/>
       <c r="X46" s="54"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24">
       <c r="A47" s="5" t="s">
         <v>138</v>
       </c>
@@ -54301,7 +54317,7 @@
       <c r="W47" s="90"/>
       <c r="X47" s="90"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24">
       <c r="A48" s="6"/>
       <c r="B48" s="52" t="s">
         <v>64</v>
@@ -54373,7 +54389,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -54468,7 +54484,7 @@
         <v>152561.58882474885</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -54562,7 +54578,7 @@
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -54657,7 +54673,7 @@
         <v>88485.72151835433</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -54754,7 +54770,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>92</v>
       </c>
@@ -54848,7 +54864,7 @@
         <v>22884.238323712325</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -54945,7 +54961,7 @@
         <v>65601.483194642002</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>94</v>
       </c>
@@ -55042,7 +55058,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>130</v>
       </c>
@@ -55139,7 +55155,7 @@
         <v>13776.31147087482</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>96</v>
       </c>
@@ -55236,7 +55252,7 @@
         <v>51825.171723767184</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24">
       <c r="A58" t="s">
         <v>97</v>
       </c>
@@ -55333,7 +55349,7 @@
         <v>22884.238323712325</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -55427,7 +55443,7 @@
         <v>-22884.238323712325</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24">
       <c r="A60" t="s">
         <v>99</v>
       </c>
@@ -55521,7 +55537,7 @@
         <v>-108.97256344624911</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24">
       <c r="A61" s="19" t="s">
         <v>100</v>
       </c>
@@ -55618,7 +55634,7 @@
         <v>51716.199160320932</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24">
       <c r="A62" t="s">
         <v>101</v>
       </c>
@@ -55715,7 +55731,7 @@
         <v>0.33898571428571428</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24">
       <c r="B63" s="54"/>
       <c r="C63" s="54"/>
       <c r="D63" s="54"/>
@@ -55740,7 +55756,7 @@
       <c r="W63" s="54"/>
       <c r="X63" s="54"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24">
       <c r="A64" s="5" t="s">
         <v>102</v>
       </c>
@@ -55768,7 +55784,7 @@
       <c r="W64" s="97"/>
       <c r="X64" s="97"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24">
       <c r="A65" s="6" t="s">
         <v>139</v>
       </c>
@@ -55836,7 +55852,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24">
       <c r="A66" t="s">
         <v>103</v>
       </c>
@@ -55904,7 +55920,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24">
       <c r="A67" t="s">
         <v>104</v>
       </c>
@@ -55992,7 +56008,7 @@
         <v>0.11793952759208834</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24">
       <c r="A68" t="s">
         <v>105</v>
       </c>
@@ -56080,7 +56096,7 @@
         <v>51716.199160320932</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24">
       <c r="A69" t="s">
         <v>106</v>
       </c>
@@ -56168,7 +56184,7 @@
         <v>6099.3840978266062</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24">
       <c r="B70" s="54"/>
       <c r="C70" s="54"/>
       <c r="D70" s="54"/>
@@ -56193,7 +56209,7 @@
       <c r="W70" s="54"/>
       <c r="X70" s="54"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24">
       <c r="A71" s="5" t="s">
         <v>107</v>
       </c>
@@ -56221,7 +56237,7 @@
       <c r="W71" s="90"/>
       <c r="X71" s="90"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24">
       <c r="A72" s="1" t="s">
         <v>108</v>
       </c>
@@ -56249,7 +56265,7 @@
       <c r="W72" s="54"/>
       <c r="X72" s="54"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24">
       <c r="A73" t="s">
         <v>131</v>
       </c>
@@ -56280,7 +56296,7 @@
       <c r="W73" s="54"/>
       <c r="X73" s="54"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -56311,7 +56327,7 @@
       <c r="W74" s="54"/>
       <c r="X74" s="54"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -56342,7 +56358,7 @@
       <c r="W75" s="54"/>
       <c r="X75" s="54"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -56373,7 +56389,7 @@
       <c r="W76" s="54"/>
       <c r="X76" s="54"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24">
       <c r="B77" s="64"/>
       <c r="C77" s="64"/>
       <c r="D77" s="64"/>
@@ -56398,7 +56414,7 @@
       <c r="W77" s="54"/>
       <c r="X77" s="54"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24">
       <c r="A78" s="1" t="s">
         <v>140</v>
       </c>
@@ -56426,7 +56442,7 @@
       <c r="W78" s="54"/>
       <c r="X78" s="54"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24">
       <c r="A79" t="s">
         <v>788</v>
       </c>
@@ -56460,7 +56476,7 @@
       <c r="W79" s="54"/>
       <c r="X79" s="54"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24">
       <c r="A80" t="s">
         <v>141</v>
       </c>
@@ -56491,7 +56507,7 @@
       <c r="W80" s="54"/>
       <c r="X80" s="54"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24">
       <c r="A81" t="s">
         <v>142</v>
       </c>
@@ -56522,7 +56538,7 @@
       <c r="W81" s="54"/>
       <c r="X81" s="54"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24">
       <c r="A82" t="s">
         <v>143</v>
       </c>
@@ -56533,12 +56549,12 @@
       <c r="C82" s="40"/>
       <c r="D82" s="40"/>
     </row>
-    <row r="83" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:24" ht="15" thickBot="1">
       <c r="B83" s="82"/>
       <c r="C83" s="40"/>
       <c r="D83" s="40"/>
     </row>
-    <row r="84" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" ht="15" thickTop="1">
       <c r="A84" s="9" t="s">
         <v>144</v>
       </c>
@@ -56546,7 +56562,7 @@
       <c r="C84" s="42"/>
       <c r="D84" s="83"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24">
       <c r="A85" s="10"/>
       <c r="B85" s="112" t="s">
         <v>259</v>
@@ -56556,7 +56572,7 @@
       </c>
       <c r="D85" s="84"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24">
       <c r="A86" s="11" t="s">
         <v>120</v>
       </c>
@@ -56570,7 +56586,7 @@
       </c>
       <c r="D86" s="40"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24">
       <c r="A87" s="11" t="s">
         <v>121</v>
       </c>
@@ -56584,7 +56600,7 @@
       </c>
       <c r="D87" s="40"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24">
       <c r="A88" s="20" t="s">
         <v>122</v>
       </c>
@@ -56598,13 +56614,13 @@
       </c>
       <c r="D88" s="40"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24">
       <c r="A89" s="11"/>
       <c r="B89" s="64"/>
       <c r="C89" s="109"/>
       <c r="D89" s="26"/>
     </row>
-    <row r="90" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:24" ht="15" thickBot="1">
       <c r="A90" s="12" t="s">
         <v>123</v>
       </c>
@@ -56617,8 +56633,8 @@
         <v>1.3636805655553659</v>
       </c>
     </row>
-    <row r="91" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" ht="15" thickTop="1"/>
+    <row r="92" spans="1:24">
       <c r="A92" s="5" t="s">
         <v>145</v>
       </c>
@@ -56646,12 +56662,12 @@
       <c r="W92" s="5"/>
       <c r="X92" s="5"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24">
       <c r="A94" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24">
       <c r="B96" s="66" t="s">
         <v>134</v>
       </c>
@@ -56676,7 +56692,7 @@
         <v>4.5000000000000005E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="B97" s="114">
         <f>$B$45-0.02</f>
         <v>9.5853579916144765E-2</v>
@@ -56702,7 +56718,7 @@
         <v>168742.80597470744</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="B98" s="114">
         <f>$B$45-0.01</f>
         <v>0.10585357991614477</v>
@@ -56728,7 +56744,7 @@
         <v>109086.37787254018</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="B99" s="114">
         <f>$B$45</f>
         <v>0.11585357991614477</v>
@@ -56754,7 +56770,7 @@
         <v>69135.562544798842</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="B100" s="114">
         <f>$B$45+0.01</f>
         <v>0.12585357991614476</v>
@@ -56780,7 +56796,7 @@
         <v>41262.07728791306</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="B101" s="114">
         <f>$B$45+0.02</f>
         <v>0.13585357991614477</v>
@@ -56806,7 +56822,7 @@
         <v>21235.780086269289</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="B102" s="54"/>
       <c r="C102" s="54"/>
       <c r="D102" s="54"/>
@@ -56814,7 +56830,7 @@
       <c r="F102" s="54"/>
       <c r="G102" s="54"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="B103" s="54"/>
       <c r="C103" s="54"/>
       <c r="D103" s="54"/>
@@ -56822,7 +56838,7 @@
       <c r="F103" s="54"/>
       <c r="G103" s="54"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="21" t="s">
         <v>146</v>
       </c>
@@ -56833,7 +56849,7 @@
       <c r="F104" s="54"/>
       <c r="G104" s="54"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="B105" s="54"/>
       <c r="C105" s="54"/>
       <c r="D105" s="54"/>
@@ -56841,7 +56857,7 @@
       <c r="F105" s="54"/>
       <c r="G105" s="54"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="B106" s="66" t="s">
         <v>147</v>
       </c>
@@ -56866,7 +56882,7 @@
         <v>7.2301136363636367</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="B107" s="114">
         <f>$B$45-0.02</f>
         <v>9.5853579916144765E-2</v>
@@ -56892,7 +56908,7 @@
         <v>175507.5996414882</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="B108" s="114">
         <f>$B$45-0.01</f>
         <v>0.10585357991614477</v>
@@ -56918,7 +56934,7 @@
         <v>139301.88008664543</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="B109" s="114">
         <f>$B$45</f>
         <v>0.11585357991614477</v>
@@ -56944,7 +56960,7 @@
         <v>109269.15710329358</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="B110" s="114">
         <f>$B$45+0.01</f>
         <v>0.12585357991614476</v>
@@ -56970,7 +56986,7 @@
         <v>84336.448615190049</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="B111" s="114">
         <f>$B$45+0.02</f>
         <v>0.13585357991614477</v>
@@ -56996,7 +57012,7 @@
         <v>63624.078818490721</v>
       </c>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24">
       <c r="A124" s="350" t="s">
         <v>277</v>
       </c>
@@ -57024,7 +57040,7 @@
       <c r="W124" s="350"/>
       <c r="X124" s="350"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
         <v>266</v>
       </c>
@@ -57094,7 +57110,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24">
       <c r="A126" t="s">
         <v>278</v>
       </c>
@@ -57163,7 +57179,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24">
       <c r="A127" t="s">
         <v>279</v>
       </c>
@@ -57232,7 +57248,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24">
       <c r="A128" t="s">
         <v>280</v>
       </c>
@@ -57322,7 +57338,7 @@
         <v>24960</v>
       </c>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24">
       <c r="A129" t="s">
         <v>281</v>
       </c>
@@ -57391,7 +57407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24">
       <c r="A130" t="s">
         <v>282</v>
       </c>
@@ -57481,7 +57497,7 @@
         <v>49920</v>
       </c>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24">
       <c r="A131" t="s">
         <v>283</v>
       </c>
@@ -57570,7 +57586,7 @@
         <v>29837.564809158888</v>
       </c>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24">
       <c r="A132" t="s">
         <v>273</v>
       </c>
@@ -57637,7 +57653,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24">
       <c r="A133" s="1" t="s">
         <v>274</v>
       </c>
@@ -57728,7 +57744,7 @@
         <v>79757.564809158881</v>
       </c>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24">
       <c r="A134" t="s">
         <v>284</v>
       </c>
@@ -57818,7 +57834,7 @@
         <v>152561.58882474885</v>
       </c>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24">
       <c r="A135" s="2" t="s">
         <v>276</v>
       </c>
@@ -57923,7 +57939,7 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="5" width="11.109375" customWidth="1"/>
@@ -57932,18 +57948,18 @@
     <col min="8" max="14" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="15" thickBot="1"/>
+    <row r="4" spans="1:6" ht="15" thickTop="1">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -57953,7 +57969,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
@@ -57967,7 +57983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="11" t="s">
         <v>9</v>
       </c>
@@ -57981,7 +57997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
@@ -57995,7 +58011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
@@ -58009,7 +58025,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" thickBot="1">
       <c r="A9" s="12" t="s">
         <v>786</v>
       </c>
@@ -58023,14 +58039,14 @@
         <v>789</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15.6" thickTop="1" thickBot="1">
       <c r="A10" s="330"/>
       <c r="B10" s="331"/>
       <c r="C10" s="54"/>
       <c r="D10" s="54"/>
       <c r="E10" s="54"/>
     </row>
-    <row r="11" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="15" thickTop="1">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -58040,7 +58056,7 @@
       <c r="E11" s="58"/>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="10" t="s">
         <v>2</v>
       </c>
@@ -58060,7 +58076,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="11" t="s">
         <v>20</v>
       </c>
@@ -58081,7 +58097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="11" t="s">
         <v>22</v>
       </c>
@@ -58102,7 +58118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="11" t="s">
         <v>23</v>
       </c>
@@ -58123,7 +58139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -58144,7 +58160,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -58165,7 +58181,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -58186,7 +58202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="15" thickBot="1">
       <c r="A19" s="12" t="s">
         <v>31</v>
       </c>
@@ -58207,13 +58223,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="15.6" thickTop="1" thickBot="1">
       <c r="B20" s="63"/>
       <c r="C20" s="63"/>
       <c r="D20" s="64"/>
       <c r="E20" s="63"/>
     </row>
-    <row r="21" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15" thickTop="1">
       <c r="A21" s="15" t="s">
         <v>564</v>
       </c>
@@ -58223,7 +58239,7 @@
       <c r="E21" s="65"/>
       <c r="F21" s="17"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="16" t="s">
         <v>19</v>
       </c>
@@ -58237,7 +58253,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="11" t="s">
         <v>35</v>
       </c>
@@ -58252,7 +58268,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="11" t="s">
         <v>36</v>
       </c>
@@ -58267,7 +58283,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="15" thickBot="1">
       <c r="A25" s="12" t="s">
         <v>37</v>
       </c>
@@ -58282,13 +58298,13 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="15.6" thickTop="1" thickBot="1">
       <c r="B26" s="54"/>
       <c r="C26" s="54"/>
       <c r="D26" s="54"/>
       <c r="E26" s="54"/>
     </row>
-    <row r="27" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15" thickTop="1">
       <c r="A27" s="9" t="s">
         <v>38</v>
       </c>
@@ -58298,7 +58314,7 @@
       <c r="E27" s="58"/>
       <c r="F27" s="13"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="10"/>
       <c r="B28" s="52" t="s">
         <v>39</v>
@@ -58314,7 +58330,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="11" t="s">
         <v>42</v>
       </c>
@@ -58332,7 +58348,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="11" t="s">
         <v>44</v>
       </c>
@@ -58353,7 +58369,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15" thickBot="1">
       <c r="A31" s="12" t="s">
         <v>46</v>
       </c>
@@ -58374,13 +58390,13 @@
         <v>787</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="15.6" thickTop="1" thickBot="1">
       <c r="B32" s="54"/>
       <c r="C32" s="54"/>
       <c r="D32" s="54"/>
       <c r="E32" s="54"/>
     </row>
-    <row r="33" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="15" thickTop="1">
       <c r="A33" s="9" t="s">
         <v>47</v>
       </c>
@@ -58390,7 +58406,7 @@
       <c r="E33" s="58"/>
       <c r="F33" s="13"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="10"/>
       <c r="B34" s="52" t="s">
         <v>39</v>
@@ -58406,7 +58422,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="11" t="s">
         <v>48</v>
       </c>
@@ -58424,7 +58440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="15" thickBot="1">
       <c r="A36" s="12" t="s">
         <v>50</v>
       </c>
@@ -58445,19 +58461,19 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="15" thickTop="1">
       <c r="B37" s="54"/>
       <c r="C37" s="54"/>
       <c r="D37" s="54"/>
       <c r="E37" s="54"/>
     </row>
-    <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="15" thickBot="1">
       <c r="B38" s="54"/>
       <c r="C38" s="54"/>
       <c r="D38" s="54"/>
       <c r="E38" s="54"/>
     </row>
-    <row r="39" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="15" thickTop="1">
       <c r="A39" s="9" t="s">
         <v>52</v>
       </c>
@@ -58467,7 +58483,7 @@
       <c r="E39" s="58"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="10"/>
       <c r="B40" s="60" t="s">
         <v>39</v>
@@ -58481,7 +58497,7 @@
       <c r="E40" s="52"/>
       <c r="F40" s="14"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="11" t="s">
         <v>53</v>
       </c>
@@ -58502,7 +58518,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" s="11" t="s">
         <v>55</v>
       </c>
@@ -58523,7 +58539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15" thickBot="1">
       <c r="A43" s="18" t="s">
         <v>57</v>
       </c>
@@ -58544,13 +58560,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="15.6" thickTop="1" thickBot="1">
       <c r="B44" s="54"/>
       <c r="C44" s="54"/>
       <c r="D44" s="54"/>
       <c r="E44" s="54"/>
     </row>
-    <row r="45" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="15" thickTop="1">
       <c r="A45" s="9" t="s">
         <v>59</v>
       </c>
@@ -58560,7 +58576,7 @@
       <c r="E45" s="58"/>
       <c r="F45" s="13"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" s="10" t="s">
         <v>19</v>
       </c>
@@ -58578,7 +58594,7 @@
       </c>
       <c r="F46" s="14"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" s="11" t="s">
         <v>39</v>
       </c>
@@ -58597,7 +58613,7 @@
       </c>
       <c r="F47" s="36"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" s="11" t="s">
         <v>24</v>
       </c>
@@ -58616,7 +58632,7 @@
       </c>
       <c r="F48" s="36"/>
     </row>
-    <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="15" thickBot="1">
       <c r="A49" s="12" t="s">
         <v>40</v>
       </c>
@@ -58635,14 +58651,14 @@
       </c>
       <c r="F49" s="37"/>
     </row>
-    <row r="50" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="15" thickTop="1">
       <c r="B50" s="35"/>
       <c r="C50" s="33"/>
       <c r="D50" s="33"/>
       <c r="E50" s="33"/>
       <c r="F50" s="33"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="B51" s="35"/>
       <c r="C51" s="33"/>
       <c r="D51" s="33"/>
@@ -58661,33 +58677,33 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.5546875" customWidth="1"/>
     <col min="2" max="6" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" s="46" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="350" t="s">
         <v>318</v>
       </c>
-      <c r="B4" s="351"/>
-      <c r="C4" s="351"/>
-      <c r="D4" s="351"/>
-      <c r="E4" s="351"/>
-      <c r="F4" s="351"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="352"/>
+      <c r="C4" s="352"/>
+      <c r="D4" s="352"/>
+      <c r="E4" s="352"/>
+      <c r="F4" s="352"/>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>319</v>
       </c>
@@ -58696,7 +58712,7 @@
         <v>576167.18807757646</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>320</v>
       </c>
@@ -58705,7 +58721,7 @@
         <v>574706.18807757646</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>321</v>
       </c>
@@ -58714,7 +58730,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>322</v>
       </c>
@@ -58723,7 +58739,7 @@
         <v>12960</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>323</v>
       </c>
@@ -58732,7 +58748,7 @@
         <v>1749600</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>324</v>
       </c>
@@ -58741,7 +58757,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>325</v>
       </c>
@@ -58750,17 +58766,17 @@
         <v>1748139</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="350" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="351"/>
-      <c r="C13" s="351"/>
-      <c r="D13" s="351"/>
-      <c r="E13" s="351"/>
-      <c r="F13" s="351"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="352"/>
+      <c r="C13" s="352"/>
+      <c r="D13" s="352"/>
+      <c r="E13" s="352"/>
+      <c r="F13" s="352"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -58769,7 +58785,7 @@
         <v>18674</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>327</v>
       </c>
@@ -58778,7 +58794,7 @@
         <v>11387</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>328</v>
       </c>
@@ -58787,7 +58803,7 @@
         <v>4086</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>329</v>
       </c>
@@ -58796,7 +58812,7 @@
         <v>3201</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>330</v>
       </c>
@@ -58804,7 +58820,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>331</v>
       </c>
@@ -58813,7 +58829,7 @@
         <v>7168</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>186</v>
       </c>
@@ -58822,17 +58838,17 @@
         <v>-4937</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="350" t="s">
         <v>332</v>
       </c>
-      <c r="B22" s="351"/>
-      <c r="C22" s="351"/>
-      <c r="D22" s="351"/>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="352"/>
+      <c r="C22" s="352"/>
+      <c r="D22" s="352"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="6" t="s">
         <v>3</v>
       </c>
@@ -58848,7 +58864,7 @@
       </c>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>336</v>
       </c>
@@ -58865,7 +58881,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>338</v>
       </c>
@@ -58882,7 +58898,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>340</v>
       </c>
@@ -58899,7 +58915,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>342</v>
       </c>
@@ -58916,7 +58932,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>344</v>
       </c>
@@ -58931,7 +58947,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>347</v>
       </c>
@@ -58948,17 +58964,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="350" t="s">
         <v>348</v>
       </c>
-      <c r="B31" s="351"/>
-      <c r="C31" s="351"/>
-      <c r="D31" s="351"/>
-      <c r="E31" s="351"/>
-      <c r="F31" s="351"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="352"/>
+      <c r="C31" s="352"/>
+      <c r="D31" s="352"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>349</v>
       </c>
@@ -58966,7 +58982,7 @@
         <v>24747</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>350</v>
       </c>
@@ -58974,7 +58990,7 @@
         <v>30952</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>351</v>
       </c>
@@ -58982,7 +58998,7 @@
         <v>92079</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>352</v>
       </c>
@@ -58990,7 +59006,7 @@
         <v>21400</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>353</v>
       </c>
@@ -58998,7 +59014,7 @@
         <v>23286</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>354</v>
       </c>
@@ -59006,7 +59022,7 @@
         <v>50754</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>355</v>
       </c>
@@ -59014,17 +59030,17 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="350" t="s">
         <v>356</v>
       </c>
-      <c r="B40" s="351"/>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="352"/>
+      <c r="C40" s="352"/>
+      <c r="D40" s="352"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="6" t="s">
         <v>357</v>
       </c>
@@ -59038,7 +59054,7 @@
       </c>
       <c r="F41" s="52"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>358</v>
       </c>
@@ -59053,7 +59069,7 @@
       </c>
       <c r="F42" s="54"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>360</v>
       </c>
@@ -59068,7 +59084,7 @@
       </c>
       <c r="F43" s="54"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>362</v>
       </c>
@@ -59083,7 +59099,7 @@
       </c>
       <c r="F44" s="54"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>364</v>
       </c>
@@ -59098,7 +59114,7 @@
       </c>
       <c r="F45" s="54"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>366</v>
       </c>
@@ -59113,7 +59129,7 @@
       </c>
       <c r="F46" s="54"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>368</v>
       </c>
@@ -59128,7 +59144,7 @@
       </c>
       <c r="F47" s="54"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>370</v>
       </c>
@@ -59143,7 +59159,7 @@
       </c>
       <c r="F48" s="54"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>372</v>
       </c>
@@ -59158,7 +59174,7 @@
       </c>
       <c r="F49" s="54"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>374</v>
       </c>
@@ -59173,7 +59189,7 @@
       </c>
       <c r="F50" s="54"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>376</v>
       </c>
@@ -59188,7 +59204,7 @@
       </c>
       <c r="F51" s="54"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="E52" s="81"/>
     </row>
   </sheetData>
@@ -59210,19 +59226,19 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:X10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="10.5546875" customWidth="1"/>
     <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="30" customHeight="1">
       <c r="A1" s="324" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24">
       <c r="T3" s="1" t="s">
         <v>291</v>
       </c>
@@ -59230,7 +59246,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24">
       <c r="T4" t="s">
         <v>19</v>
       </c>
@@ -59244,7 +59260,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24">
       <c r="T5" t="s">
         <v>39</v>
       </c>
@@ -59259,7 +59275,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24">
       <c r="T6" t="s">
         <v>24</v>
       </c>
@@ -59274,7 +59290,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="T7" t="s">
         <v>40</v>
       </c>
@@ -59289,7 +59305,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="W8" t="s">
         <v>295</v>
       </c>
@@ -59297,7 +59313,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24">
       <c r="W9" t="s">
         <v>412</v>
       </c>
@@ -59306,7 +59322,7 @@
         <v>649.14863953638405</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24">
       <c r="W10" t="s">
         <v>411</v>
       </c>

--- a/07_Model/SpaceX Valuation Model v26.06.11 (Pre-IPO).xlsx
+++ b/07_Model/SpaceX Valuation Model v26.06.11 (Pre-IPO).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Personal Finances\4-Trades &amp; Investments\Valuation Models\$SPCX - Space Exploration Technologies Corp\07_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B520D8-C626-436F-A73D-F3577D97866F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DC140B-610F-4341-A95D-8F6BFD033224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="877" xr2:uid="{80111FE1-D860-9C46-9D05-D269D00C2A2F}"/>
   </bookViews>
@@ -19607,7 +19607,7 @@
     <t>Comp Data Status</t>
   </si>
   <si>
-    <t>Rifat Tahmid</t>
+    <t>Property of Rifat Tahmid</t>
   </si>
 </sst>
 </file>
@@ -21237,35 +21237,35 @@
     <xf numFmtId="0" fontId="76" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="68" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -23512,33 +23512,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="345" t="s">
+      <c r="A1" s="343" t="s">
         <v>763</v>
       </c>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
+      <c r="B1" s="344"/>
+      <c r="C1" s="344"/>
+      <c r="D1" s="344"/>
+      <c r="E1" s="344"/>
+      <c r="F1" s="344"/>
+      <c r="G1" s="344"/>
+      <c r="H1" s="344"/>
+      <c r="I1" s="344"/>
+      <c r="J1" s="344"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="347" t="str">
+      <c r="A2" s="345" t="str">
         <f ca="1">"Prepared: "&amp;TEXT(TODAY(),"d-mmm-yyyy")&amp;"  |  Source: SpaceX S-1 (Filed 20-May-2026) "</f>
         <v xml:space="preserve">Prepared: 11-Jun-2026  |  Source: SpaceX S-1 (Filed 20-May-2026) </v>
       </c>
-      <c r="B2" s="348"/>
-      <c r="C2" s="348"/>
-      <c r="D2" s="348"/>
-      <c r="E2" s="348"/>
-      <c r="F2" s="348"/>
-      <c r="G2" s="348"/>
-      <c r="H2" s="348"/>
-      <c r="I2" s="348"/>
-      <c r="J2" s="348"/>
+      <c r="B2" s="346"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
+      <c r="I2" s="346"/>
+      <c r="J2" s="346"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="252"/>
@@ -24641,26 +24641,26 @@
       <c r="F69" s="252"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="340" t="s">
+      <c r="A70" s="349" t="s">
         <v>741</v>
       </c>
-      <c r="B70" s="340"/>
-      <c r="C70" s="340" t="s">
+      <c r="B70" s="349"/>
+      <c r="C70" s="349" t="s">
         <v>742</v>
       </c>
-      <c r="D70" s="340"/>
-      <c r="E70" s="340"/>
-      <c r="F70" s="340"/>
-      <c r="G70" s="340"/>
-      <c r="H70" s="340"/>
-      <c r="I70" s="340"/>
-      <c r="J70" s="340"/>
+      <c r="D70" s="349"/>
+      <c r="E70" s="349"/>
+      <c r="F70" s="349"/>
+      <c r="G70" s="349"/>
+      <c r="H70" s="349"/>
+      <c r="I70" s="349"/>
+      <c r="J70" s="349"/>
     </row>
     <row r="71" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A71" s="344" t="s">
+      <c r="A71" s="347" t="s">
         <v>743</v>
       </c>
-      <c r="B71" s="344"/>
+      <c r="B71" s="347"/>
       <c r="C71" s="341" t="s">
         <v>744</v>
       </c>
@@ -24673,10 +24673,10 @@
       <c r="J71" s="341"/>
     </row>
     <row r="72" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A72" s="344" t="s">
+      <c r="A72" s="347" t="s">
         <v>745</v>
       </c>
-      <c r="B72" s="344"/>
+      <c r="B72" s="347"/>
       <c r="C72" s="341" t="s">
         <v>746</v>
       </c>
@@ -24689,10 +24689,10 @@
       <c r="J72" s="341"/>
     </row>
     <row r="73" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A73" s="344" t="s">
+      <c r="A73" s="347" t="s">
         <v>747</v>
       </c>
-      <c r="B73" s="344"/>
+      <c r="B73" s="347"/>
       <c r="C73" s="341" t="s">
         <v>748</v>
       </c>
@@ -24705,10 +24705,10 @@
       <c r="J73" s="341"/>
     </row>
     <row r="74" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A74" s="344" t="s">
+      <c r="A74" s="347" t="s">
         <v>749</v>
       </c>
-      <c r="B74" s="344"/>
+      <c r="B74" s="347"/>
       <c r="C74" s="341" t="s">
         <v>750</v>
       </c>
@@ -24721,10 +24721,10 @@
       <c r="J74" s="341"/>
     </row>
     <row r="75" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A75" s="344" t="s">
+      <c r="A75" s="347" t="s">
         <v>751</v>
       </c>
-      <c r="B75" s="344"/>
+      <c r="B75" s="347"/>
       <c r="C75" s="341" t="s">
         <v>752</v>
       </c>
@@ -24737,10 +24737,10 @@
       <c r="J75" s="341"/>
     </row>
     <row r="76" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A76" s="344" t="s">
+      <c r="A76" s="347" t="s">
         <v>57</v>
       </c>
-      <c r="B76" s="344"/>
+      <c r="B76" s="347"/>
       <c r="C76" s="341" t="s">
         <v>753</v>
       </c>
@@ -24753,10 +24753,10 @@
       <c r="J76" s="341"/>
     </row>
     <row r="77" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A77" s="344" t="s">
+      <c r="A77" s="347" t="s">
         <v>754</v>
       </c>
-      <c r="B77" s="344"/>
+      <c r="B77" s="347"/>
       <c r="C77" s="341" t="s">
         <v>755</v>
       </c>
@@ -24769,10 +24769,10 @@
       <c r="J77" s="341"/>
     </row>
     <row r="78" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A78" s="344" t="s">
+      <c r="A78" s="347" t="s">
         <v>756</v>
       </c>
-      <c r="B78" s="344"/>
+      <c r="B78" s="347"/>
       <c r="C78" s="341" t="s">
         <v>757</v>
       </c>
@@ -24785,10 +24785,10 @@
       <c r="J78" s="341"/>
     </row>
     <row r="79" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A79" s="344" t="s">
+      <c r="A79" s="347" t="s">
         <v>758</v>
       </c>
-      <c r="B79" s="344"/>
+      <c r="B79" s="347"/>
       <c r="C79" s="341" t="s">
         <v>759</v>
       </c>
@@ -24801,43 +24801,63 @@
       <c r="J79" s="341"/>
     </row>
     <row r="80" spans="1:10" ht="14.4" customHeight="1">
-      <c r="A80" s="349" t="s">
+      <c r="A80" s="348" t="s">
         <v>760</v>
       </c>
-      <c r="B80" s="349"/>
-      <c r="C80" s="343" t="s">
+      <c r="B80" s="348"/>
+      <c r="C80" s="342" t="s">
         <v>761</v>
       </c>
-      <c r="D80" s="343"/>
-      <c r="E80" s="343"/>
-      <c r="F80" s="343"/>
-      <c r="G80" s="343"/>
-      <c r="H80" s="343"/>
-      <c r="I80" s="343"/>
-      <c r="J80" s="343"/>
+      <c r="D80" s="342"/>
+      <c r="E80" s="342"/>
+      <c r="F80" s="342"/>
+      <c r="G80" s="342"/>
+      <c r="H80" s="342"/>
+      <c r="I80" s="342"/>
+      <c r="J80" s="342"/>
     </row>
     <row r="81" spans="1:10" ht="14.4" customHeight="1"/>
     <row r="82" spans="1:10" ht="21.6" customHeight="1">
-      <c r="A82" s="342" t="s">
+      <c r="A82" s="350" t="s">
         <v>762</v>
       </c>
-      <c r="B82" s="342"/>
-      <c r="C82" s="342"/>
-      <c r="D82" s="342"/>
-      <c r="E82" s="342"/>
-      <c r="F82" s="342"/>
-      <c r="G82" s="342"/>
-      <c r="H82" s="342"/>
-      <c r="I82" s="342"/>
-      <c r="J82" s="342"/>
+      <c r="B82" s="350"/>
+      <c r="C82" s="350"/>
+      <c r="D82" s="350"/>
+      <c r="E82" s="350"/>
+      <c r="F82" s="350"/>
+      <c r="G82" s="350"/>
+      <c r="H82" s="350"/>
+      <c r="I82" s="350"/>
+      <c r="J82" s="350"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="356" t="s">
+      <c r="A100" s="340" t="s">
         <v>791</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G71:J71"/>
+    <mergeCell ref="G72:J72"/>
+    <mergeCell ref="G73:J73"/>
+    <mergeCell ref="G74:J74"/>
+    <mergeCell ref="G75:J75"/>
+    <mergeCell ref="G76:J76"/>
+    <mergeCell ref="C80:F80"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="G77:J77"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="C73:F73"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="G80:J80"/>
@@ -24854,26 +24874,6 @@
     <mergeCell ref="C78:F78"/>
     <mergeCell ref="C79:F79"/>
     <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="G77:J77"/>
-    <mergeCell ref="C70:F70"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="C72:F72"/>
-    <mergeCell ref="C73:F73"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G71:J71"/>
-    <mergeCell ref="G72:J72"/>
-    <mergeCell ref="G73:J73"/>
-    <mergeCell ref="G74:J74"/>
-    <mergeCell ref="G75:J75"/>
-    <mergeCell ref="G76:J76"/>
-    <mergeCell ref="C80:F80"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A72:B72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -34486,7 +34486,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="351" t="s">
         <v>390</v>
       </c>
       <c r="B4" s="352"/>
@@ -34787,16 +34787,16 @@
       <c r="G16" s="54"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="355" t="s">
+      <c r="A18" s="356" t="s">
         <v>392</v>
       </c>
-      <c r="B18" s="355"/>
-      <c r="C18" s="355"/>
-      <c r="D18" s="355"/>
-      <c r="E18" s="355"/>
-      <c r="F18" s="355"/>
-      <c r="G18" s="355"/>
-      <c r="H18" s="355"/>
+      <c r="B18" s="356"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+      <c r="G18" s="356"/>
+      <c r="H18" s="356"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="6" t="s">
@@ -34939,16 +34939,16 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="355" t="s">
+      <c r="A26" s="356" t="s">
         <v>397</v>
       </c>
-      <c r="B26" s="355"/>
-      <c r="C26" s="355"/>
-      <c r="D26" s="355"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
-      <c r="G26" s="355"/>
-      <c r="H26" s="355"/>
+      <c r="B26" s="356"/>
+      <c r="C26" s="356"/>
+      <c r="D26" s="356"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
+      <c r="G26" s="356"/>
+      <c r="H26" s="356"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="6" t="s">
@@ -35159,16 +35159,16 @@
       <c r="H36" s="54"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="355" t="s">
+      <c r="A38" s="356" t="s">
         <v>402</v>
       </c>
-      <c r="B38" s="355"/>
-      <c r="C38" s="355"/>
-      <c r="D38" s="355"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
-      <c r="G38" s="355"/>
-      <c r="H38" s="355"/>
+      <c r="B38" s="356"/>
+      <c r="C38" s="356"/>
+      <c r="D38" s="356"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
+      <c r="G38" s="356"/>
+      <c r="H38" s="356"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="6" t="s">
@@ -37495,46 +37495,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="345" t="s">
+      <c r="A1" s="343" t="s">
         <v>764</v>
       </c>
-      <c r="B1" s="346"/>
-      <c r="C1" s="346"/>
-      <c r="D1" s="346"/>
-      <c r="E1" s="346"/>
-      <c r="F1" s="346"/>
-      <c r="G1" s="346"/>
-      <c r="H1" s="346"/>
-      <c r="I1" s="346"/>
-      <c r="J1" s="346"/>
+      <c r="B1" s="344"/>
+      <c r="C1" s="344"/>
+      <c r="D1" s="344"/>
+      <c r="E1" s="344"/>
+      <c r="F1" s="344"/>
+      <c r="G1" s="344"/>
+      <c r="H1" s="344"/>
+      <c r="I1" s="344"/>
+      <c r="J1" s="344"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="347" t="s">
+      <c r="A2" s="345" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="348"/>
-      <c r="C2" s="348"/>
-      <c r="D2" s="348"/>
-      <c r="E2" s="348"/>
-      <c r="F2" s="348"/>
-      <c r="G2" s="348"/>
-      <c r="H2" s="348"/>
-      <c r="I2" s="348"/>
-      <c r="J2" s="348"/>
+      <c r="B2" s="346"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
+      <c r="I2" s="346"/>
+      <c r="J2" s="346"/>
     </row>
     <row r="4" spans="1:10" ht="15" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="351" t="s">
         <v>194</v>
       </c>
-      <c r="B4" s="346"/>
-      <c r="C4" s="346"/>
-      <c r="D4" s="346"/>
-      <c r="E4" s="346"/>
-      <c r="F4" s="346"/>
-      <c r="G4" s="346"/>
-      <c r="H4" s="346"/>
-      <c r="I4" s="346"/>
-      <c r="J4" s="346"/>
+      <c r="B4" s="344"/>
+      <c r="C4" s="344"/>
+      <c r="D4" s="344"/>
+      <c r="E4" s="344"/>
+      <c r="F4" s="344"/>
+      <c r="G4" s="344"/>
+      <c r="H4" s="344"/>
+      <c r="I4" s="344"/>
+      <c r="J4" s="344"/>
     </row>
     <row r="5" spans="1:10" ht="15" thickBot="1">
       <c r="A5" s="1" t="s">
@@ -37543,7 +37543,7 @@
       <c r="B5" s="32">
         <v>135</v>
       </c>
-      <c r="C5" s="351" t="s">
+      <c r="C5" s="355" t="s">
         <v>196</v>
       </c>
       <c r="D5" s="352"/>
@@ -37555,18 +37555,18 @@
       <c r="J5" s="352"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="350" t="s">
+      <c r="A7" s="351" t="s">
         <v>197</v>
       </c>
-      <c r="B7" s="346"/>
-      <c r="C7" s="346"/>
-      <c r="D7" s="346"/>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
-      <c r="G7" s="346"/>
-      <c r="H7" s="346"/>
-      <c r="I7" s="346"/>
-      <c r="J7" s="346"/>
+      <c r="B7" s="344"/>
+      <c r="C7" s="344"/>
+      <c r="D7" s="344"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
+      <c r="G7" s="344"/>
+      <c r="H7" s="344"/>
+      <c r="I7" s="344"/>
+      <c r="J7" s="344"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="6"/>
@@ -37788,18 +37788,18 @@
       <c r="J18" s="145"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="350" t="s">
+      <c r="A20" s="351" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="346"/>
-      <c r="C20" s="346"/>
-      <c r="D20" s="346"/>
-      <c r="E20" s="346"/>
-      <c r="F20" s="346"/>
-      <c r="G20" s="346"/>
-      <c r="H20" s="346"/>
-      <c r="I20" s="346"/>
-      <c r="J20" s="346"/>
+      <c r="B20" s="344"/>
+      <c r="C20" s="344"/>
+      <c r="D20" s="344"/>
+      <c r="E20" s="344"/>
+      <c r="F20" s="344"/>
+      <c r="G20" s="344"/>
+      <c r="H20" s="344"/>
+      <c r="I20" s="344"/>
+      <c r="J20" s="344"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="6"/>
@@ -37877,18 +37877,18 @@
       <c r="J24" s="150"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="350" t="s">
+      <c r="A26" s="351" t="s">
         <v>211</v>
       </c>
-      <c r="B26" s="346"/>
-      <c r="C26" s="346"/>
-      <c r="D26" s="346"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
-      <c r="G26" s="346"/>
-      <c r="H26" s="346"/>
-      <c r="I26" s="346"/>
-      <c r="J26" s="346"/>
+      <c r="B26" s="344"/>
+      <c r="C26" s="344"/>
+      <c r="D26" s="344"/>
+      <c r="E26" s="344"/>
+      <c r="F26" s="344"/>
+      <c r="G26" s="344"/>
+      <c r="H26" s="344"/>
+      <c r="I26" s="344"/>
+      <c r="J26" s="344"/>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="6" t="s">
@@ -37987,18 +37987,18 @@
       <c r="J31" s="352"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="350" t="s">
+      <c r="A33" s="351" t="s">
         <v>232</v>
       </c>
-      <c r="B33" s="346"/>
-      <c r="C33" s="346"/>
-      <c r="D33" s="346"/>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
-      <c r="G33" s="346"/>
-      <c r="H33" s="346"/>
-      <c r="I33" s="346"/>
-      <c r="J33" s="346"/>
+      <c r="B33" s="344"/>
+      <c r="C33" s="344"/>
+      <c r="D33" s="344"/>
+      <c r="E33" s="344"/>
+      <c r="F33" s="344"/>
+      <c r="G33" s="344"/>
+      <c r="H33" s="344"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="6" t="s">
@@ -38081,18 +38081,18 @@
       <c r="J37" s="150"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="350" t="s">
+      <c r="A39" s="351" t="s">
         <v>425</v>
       </c>
-      <c r="B39" s="346"/>
-      <c r="C39" s="346"/>
-      <c r="D39" s="346"/>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
-      <c r="G39" s="346"/>
-      <c r="H39" s="346"/>
-      <c r="I39" s="346"/>
-      <c r="J39" s="346"/>
+      <c r="B39" s="344"/>
+      <c r="C39" s="344"/>
+      <c r="D39" s="344"/>
+      <c r="E39" s="344"/>
+      <c r="F39" s="344"/>
+      <c r="G39" s="344"/>
+      <c r="H39" s="344"/>
+      <c r="I39" s="344"/>
+      <c r="J39" s="344"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="6" t="s">
@@ -38254,18 +38254,18 @@
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="350" t="s">
+      <c r="A48" s="351" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="346"/>
-      <c r="C48" s="346"/>
-      <c r="D48" s="346"/>
-      <c r="E48" s="346"/>
-      <c r="F48" s="346"/>
-      <c r="G48" s="346"/>
-      <c r="H48" s="346"/>
-      <c r="I48" s="346"/>
-      <c r="J48" s="346"/>
+      <c r="B48" s="344"/>
+      <c r="C48" s="344"/>
+      <c r="D48" s="344"/>
+      <c r="E48" s="344"/>
+      <c r="F48" s="344"/>
+      <c r="G48" s="344"/>
+      <c r="H48" s="344"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="6" t="s">
@@ -38456,7 +38456,7 @@
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="350" t="s">
+      <c r="A62" s="351" t="s">
         <v>311</v>
       </c>
       <c r="B62" s="352"/>
@@ -38610,6 +38610,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C5:J5"/>
+    <mergeCell ref="A7:J7"/>
     <mergeCell ref="A62:J62"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A31:J31"/>
@@ -38617,12 +38623,6 @@
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A48:J48"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C5:J5"/>
-    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -39424,15 +39424,15 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="350" t="s">
+      <c r="A48" s="351" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="350"/>
-      <c r="C48" s="350"/>
-      <c r="D48" s="350"/>
-      <c r="E48" s="350"/>
-      <c r="F48" s="350"/>
-      <c r="G48" s="350"/>
+      <c r="B48" s="351"/>
+      <c r="C48" s="351"/>
+      <c r="D48" s="351"/>
+      <c r="E48" s="351"/>
+      <c r="F48" s="351"/>
+      <c r="G48" s="351"/>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="22" t="s">
@@ -45105,32 +45105,32 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="350" t="s">
+      <c r="A124" s="351" t="s">
         <v>265</v>
       </c>
-      <c r="B124" s="350"/>
-      <c r="C124" s="350"/>
-      <c r="D124" s="350"/>
-      <c r="E124" s="350"/>
-      <c r="F124" s="350"/>
-      <c r="G124" s="350"/>
-      <c r="H124" s="350"/>
-      <c r="I124" s="350"/>
-      <c r="J124" s="350"/>
-      <c r="K124" s="350"/>
-      <c r="L124" s="350"/>
-      <c r="M124" s="350"/>
-      <c r="N124" s="350"/>
-      <c r="O124" s="350"/>
-      <c r="P124" s="350"/>
-      <c r="Q124" s="350"/>
-      <c r="R124" s="350"/>
-      <c r="S124" s="350"/>
-      <c r="T124" s="350"/>
-      <c r="U124" s="350"/>
-      <c r="V124" s="350"/>
-      <c r="W124" s="350"/>
-      <c r="X124" s="350"/>
+      <c r="B124" s="351"/>
+      <c r="C124" s="351"/>
+      <c r="D124" s="351"/>
+      <c r="E124" s="351"/>
+      <c r="F124" s="351"/>
+      <c r="G124" s="351"/>
+      <c r="H124" s="351"/>
+      <c r="I124" s="351"/>
+      <c r="J124" s="351"/>
+      <c r="K124" s="351"/>
+      <c r="L124" s="351"/>
+      <c r="M124" s="351"/>
+      <c r="N124" s="351"/>
+      <c r="O124" s="351"/>
+      <c r="P124" s="351"/>
+      <c r="Q124" s="351"/>
+      <c r="R124" s="351"/>
+      <c r="S124" s="351"/>
+      <c r="T124" s="351"/>
+      <c r="U124" s="351"/>
+      <c r="V124" s="351"/>
+      <c r="W124" s="351"/>
+      <c r="X124" s="351"/>
     </row>
     <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
@@ -51193,32 +51193,32 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="350" t="s">
+      <c r="A124" s="351" t="s">
         <v>285</v>
       </c>
-      <c r="B124" s="350"/>
-      <c r="C124" s="350"/>
-      <c r="D124" s="350"/>
-      <c r="E124" s="350"/>
-      <c r="F124" s="350"/>
-      <c r="G124" s="350"/>
-      <c r="H124" s="350"/>
-      <c r="I124" s="350"/>
-      <c r="J124" s="350"/>
-      <c r="K124" s="350"/>
-      <c r="L124" s="350"/>
-      <c r="M124" s="350"/>
-      <c r="N124" s="350"/>
-      <c r="O124" s="350"/>
-      <c r="P124" s="350"/>
-      <c r="Q124" s="350"/>
-      <c r="R124" s="350"/>
-      <c r="S124" s="350"/>
-      <c r="T124" s="350"/>
-      <c r="U124" s="350"/>
-      <c r="V124" s="350"/>
-      <c r="W124" s="350"/>
-      <c r="X124" s="350"/>
+      <c r="B124" s="351"/>
+      <c r="C124" s="351"/>
+      <c r="D124" s="351"/>
+      <c r="E124" s="351"/>
+      <c r="F124" s="351"/>
+      <c r="G124" s="351"/>
+      <c r="H124" s="351"/>
+      <c r="I124" s="351"/>
+      <c r="J124" s="351"/>
+      <c r="K124" s="351"/>
+      <c r="L124" s="351"/>
+      <c r="M124" s="351"/>
+      <c r="N124" s="351"/>
+      <c r="O124" s="351"/>
+      <c r="P124" s="351"/>
+      <c r="Q124" s="351"/>
+      <c r="R124" s="351"/>
+      <c r="S124" s="351"/>
+      <c r="T124" s="351"/>
+      <c r="U124" s="351"/>
+      <c r="V124" s="351"/>
+      <c r="W124" s="351"/>
+      <c r="X124" s="351"/>
     </row>
     <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
@@ -57013,32 +57013,32 @@
       </c>
     </row>
     <row r="124" spans="1:24">
-      <c r="A124" s="350" t="s">
+      <c r="A124" s="351" t="s">
         <v>277</v>
       </c>
-      <c r="B124" s="350"/>
-      <c r="C124" s="350"/>
-      <c r="D124" s="350"/>
-      <c r="E124" s="350"/>
-      <c r="F124" s="350"/>
-      <c r="G124" s="350"/>
-      <c r="H124" s="350"/>
-      <c r="I124" s="350"/>
-      <c r="J124" s="350"/>
-      <c r="K124" s="350"/>
-      <c r="L124" s="350"/>
-      <c r="M124" s="350"/>
-      <c r="N124" s="350"/>
-      <c r="O124" s="350"/>
-      <c r="P124" s="350"/>
-      <c r="Q124" s="350"/>
-      <c r="R124" s="350"/>
-      <c r="S124" s="350"/>
-      <c r="T124" s="350"/>
-      <c r="U124" s="350"/>
-      <c r="V124" s="350"/>
-      <c r="W124" s="350"/>
-      <c r="X124" s="350"/>
+      <c r="B124" s="351"/>
+      <c r="C124" s="351"/>
+      <c r="D124" s="351"/>
+      <c r="E124" s="351"/>
+      <c r="F124" s="351"/>
+      <c r="G124" s="351"/>
+      <c r="H124" s="351"/>
+      <c r="I124" s="351"/>
+      <c r="J124" s="351"/>
+      <c r="K124" s="351"/>
+      <c r="L124" s="351"/>
+      <c r="M124" s="351"/>
+      <c r="N124" s="351"/>
+      <c r="O124" s="351"/>
+      <c r="P124" s="351"/>
+      <c r="Q124" s="351"/>
+      <c r="R124" s="351"/>
+      <c r="S124" s="351"/>
+      <c r="T124" s="351"/>
+      <c r="U124" s="351"/>
+      <c r="V124" s="351"/>
+      <c r="W124" s="351"/>
+      <c r="X124" s="351"/>
     </row>
     <row r="125" spans="1:24">
       <c r="A125" s="6" t="s">
@@ -58694,7 +58694,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="351" t="s">
         <v>318</v>
       </c>
       <c r="B4" s="352"/>
@@ -58767,7 +58767,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="350" t="s">
+      <c r="A13" s="351" t="s">
         <v>326</v>
       </c>
       <c r="B13" s="352"/>
@@ -58839,7 +58839,7 @@
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="350" t="s">
+      <c r="A22" s="351" t="s">
         <v>332</v>
       </c>
       <c r="B22" s="352"/>
@@ -58965,7 +58965,7 @@
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="350" t="s">
+      <c r="A31" s="351" t="s">
         <v>348</v>
       </c>
       <c r="B31" s="352"/>
@@ -59031,7 +59031,7 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="350" t="s">
+      <c r="A40" s="351" t="s">
         <v>356</v>
       </c>
       <c r="B40" s="352"/>
